--- a/web/files/九龙-启德-天玺．天第2期.xlsx
+++ b/web/files/九龙-启德-天玺．天第2期.xlsx
@@ -133,13 +133,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -290,10 +290,10 @@
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -6425,12 +6425,12 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7991,38 +7991,30 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I112" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>43018800</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>47378</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K112" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L112" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K112" s="5" t="n">
+        <v>43018800</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>47378</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
@@ -8031,7 +8023,7 @@
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8128,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -8322,7 +8314,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8384,7 +8376,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8446,7 +8438,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8508,7 +8500,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8640,7 +8632,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8702,7 +8694,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -9176,7 +9168,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -9300,7 +9292,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9502,7 +9494,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9704,7 +9696,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9906,7 +9898,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9968,7 +9960,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -10030,7 +10022,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -10092,7 +10084,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -10286,7 +10278,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -10348,7 +10340,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -11576,7 +11568,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11638,7 +11630,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11700,7 +11692,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11902,7 +11894,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11959,7 +11951,7 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -11969,12 +11961,12 @@
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J172" s="3" t="inlineStr">
@@ -11984,12 +11976,12 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M172" s="3" t="inlineStr">
@@ -11999,7 +11991,7 @@
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12104,7 +12096,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -12236,7 +12228,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -12298,7 +12290,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -12360,7 +12352,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -12422,7 +12414,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -12484,7 +12476,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12616,7 +12608,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12678,7 +12670,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12740,7 +12732,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12872,7 +12864,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -13004,7 +12996,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -13136,7 +13128,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -13268,7 +13260,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -13672,7 +13664,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13944,7 +13936,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -14006,7 +13998,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -14068,7 +14060,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -14472,7 +14464,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -14674,7 +14666,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14736,7 +14728,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14798,7 +14790,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14860,7 +14852,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -15062,7 +15054,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -15404,7 +15396,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -15536,7 +15528,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -15668,7 +15660,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -15870,7 +15862,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15932,7 +15924,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -16064,7 +16056,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -16196,7 +16188,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -16258,7 +16250,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -16320,7 +16312,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -16382,7 +16374,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -16444,7 +16436,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -16646,7 +16638,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -17952,7 +17944,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -18076,7 +18068,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -18265,7 +18257,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -18275,12 +18267,12 @@
       </c>
       <c r="H267" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I267" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J267" s="3" t="inlineStr">
@@ -18290,12 +18282,12 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L267" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M267" s="3" t="inlineStr">
@@ -18305,7 +18297,7 @@
       </c>
       <c r="N267" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18340,7 +18332,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -18472,7 +18464,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -18744,7 +18736,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -18806,7 +18798,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -18868,7 +18860,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -19272,7 +19264,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -19334,7 +19326,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -19396,7 +19388,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -19458,7 +19450,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -19520,7 +19512,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -19582,7 +19574,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -19644,7 +19636,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -19776,7 +19768,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -19833,7 +19825,7 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -19843,12 +19835,12 @@
       </c>
       <c r="H291" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I291" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J291" s="3" t="inlineStr">
@@ -19858,12 +19850,12 @@
       </c>
       <c r="K291" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L291" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M291" s="3" t="inlineStr">
@@ -19873,7 +19865,7 @@
       </c>
       <c r="N291" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20048,7 +20040,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -20110,7 +20102,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -20172,7 +20164,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -20234,7 +20226,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -20296,7 +20288,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -20358,7 +20350,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -20420,7 +20412,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -20552,7 +20544,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -20676,7 +20668,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -20738,7 +20730,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -20800,7 +20792,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -20862,7 +20854,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -20924,7 +20916,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -21056,7 +21048,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -21118,7 +21110,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -21180,7 +21172,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -21312,7 +21304,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -21374,7 +21366,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -21431,38 +21423,30 @@
       </c>
       <c r="F316" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H316" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I316" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H316" s="5" t="n">
+        <v>31100000</v>
+      </c>
+      <c r="I316" s="5" t="n">
+        <v>34251</v>
       </c>
       <c r="J316" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K316" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L316" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K316" s="5" t="n">
+        <v>31100000</v>
+      </c>
+      <c r="L316" s="5" t="n">
+        <v>34251</v>
       </c>
       <c r="M316" s="3" t="inlineStr">
         <is>
@@ -21471,7 +21455,7 @@
       </c>
       <c r="N316" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -21856,7 +21840,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -22128,7 +22112,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -22610,7 +22594,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -22672,7 +22656,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -22804,7 +22788,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -22861,7 +22845,7 @@
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
@@ -23146,7 +23130,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -23208,7 +23192,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -23410,7 +23394,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -23682,7 +23666,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -23739,7 +23723,7 @@
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
@@ -24024,7 +24008,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -24151,7 +24135,7 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -24226,7 +24210,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -24498,7 +24482,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -24560,7 +24544,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -25042,7 +25026,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -25104,7 +25088,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -25656,7 +25640,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -25718,7 +25702,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -25907,31 +25891,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H382" s="5" t="n">
-        <v>15720300</v>
-      </c>
-      <c r="I382" s="5" t="n">
-        <v>32888</v>
+      <c r="H382" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I382" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="K382" s="5" t="n">
-        <v>14148270</v>
-      </c>
-      <c r="L382" s="5" t="n">
-        <v>29599</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K382" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L382" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
-          <t>360日付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N382" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26316,7 +26308,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -26378,7 +26370,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -26559,7 +26551,7 @@
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
@@ -26629,7 +26621,7 @@
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
@@ -26639,12 +26631,12 @@
       </c>
       <c r="H393" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I393" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J393" s="3" t="inlineStr">
@@ -26654,12 +26646,12 @@
       </c>
       <c r="K393" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L393" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M393" s="3" t="inlineStr">
@@ -26669,7 +26661,7 @@
       </c>
       <c r="N393" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26844,7 +26836,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -27636,7 +27628,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -27698,7 +27690,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -27884,7 +27876,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -27946,7 +27938,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -28078,7 +28070,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -28140,7 +28132,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -28272,7 +28264,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -28334,7 +28326,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -28396,7 +28388,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -28523,31 +28515,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H422" s="5" t="n">
-        <v>15403900</v>
-      </c>
-      <c r="I422" s="5" t="n">
-        <v>32226</v>
+      <c r="H422" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I422" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J422" s="3" t="inlineStr">
         <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="K422" s="5" t="n">
-        <v>14941783</v>
-      </c>
-      <c r="L422" s="5" t="n">
-        <v>31259</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K422" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L422" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M422" s="3" t="inlineStr">
         <is>
-          <t>360日付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N422" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -28792,7 +28792,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -28986,7 +28986,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -29048,7 +29048,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -29167,7 +29167,7 @@
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
@@ -29237,7 +29237,7 @@
       </c>
       <c r="F433" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G433" s="3" t="inlineStr">
@@ -29247,12 +29247,12 @@
       </c>
       <c r="H433" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I433" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J433" s="3" t="inlineStr">
@@ -29262,12 +29262,12 @@
       </c>
       <c r="K433" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L433" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M433" s="3" t="inlineStr">
@@ -29277,7 +29277,7 @@
       </c>
       <c r="N433" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -29452,7 +29452,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -29584,7 +29584,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -29848,7 +29848,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -29910,7 +29910,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -30037,38 +30037,30 @@
       </c>
       <c r="F445" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H445" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I445" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H445" s="5" t="n">
+        <v>16880000</v>
+      </c>
+      <c r="I445" s="5" t="n">
+        <v>37848</v>
       </c>
       <c r="J445" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K445" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L445" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K445" s="5" t="n">
+        <v>16880000</v>
+      </c>
+      <c r="L445" s="5" t="n">
+        <v>37848</v>
       </c>
       <c r="M445" s="3" t="inlineStr">
         <is>
@@ -30077,7 +30069,7 @@
       </c>
       <c r="N445" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -30112,7 +30104,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -30928,7 +30920,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -30990,7 +30982,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -31187,7 +31179,7 @@
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
@@ -31472,7 +31464,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -31604,7 +31596,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H468" s="5" t="n">
@@ -31666,7 +31658,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -31868,7 +31860,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -31930,7 +31922,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -32062,7 +32054,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H475" s="5" t="n">
@@ -32124,7 +32116,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -32256,7 +32248,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H478" s="5" t="n">
@@ -32318,7 +32310,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H479" s="5" t="n">
@@ -32515,7 +32507,7 @@
       </c>
       <c r="F482" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G482" s="3" t="inlineStr">
@@ -32525,12 +32517,12 @@
       </c>
       <c r="H482" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I482" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J482" s="3" t="inlineStr">
@@ -32540,12 +32532,12 @@
       </c>
       <c r="K482" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L482" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M482" s="3" t="inlineStr">
@@ -32555,7 +32547,7 @@
       </c>
       <c r="N482" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32940,7 +32932,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -33002,7 +32994,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H489" s="5" t="n">
@@ -33064,7 +33056,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H490" s="5" t="n">
@@ -33468,7 +33460,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -33600,7 +33592,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H498" s="5" t="n">
@@ -33662,7 +33654,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H499" s="5" t="n">
@@ -33724,7 +33716,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H500" s="5" t="n">
@@ -33786,7 +33778,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
@@ -34268,7 +34260,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H508" s="5" t="n">
@@ -34330,7 +34322,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H509" s="5" t="n">
@@ -34392,7 +34384,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H510" s="5" t="n">
@@ -34454,7 +34446,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H511" s="5" t="n">
@@ -34516,7 +34508,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H512" s="5" t="n">
@@ -34573,38 +34565,30 @@
       </c>
       <c r="F513" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H513" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I513" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H513" s="5" t="n">
+        <v>18998000</v>
+      </c>
+      <c r="I513" s="5" t="n">
+        <v>34859</v>
       </c>
       <c r="J513" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K513" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L513" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K513" s="5" t="n">
+        <v>18998000</v>
+      </c>
+      <c r="L513" s="5" t="n">
+        <v>34859</v>
       </c>
       <c r="M513" s="3" t="inlineStr">
         <is>
@@ -34613,7 +34597,7 @@
       </c>
       <c r="N513" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -34718,7 +34702,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H515" s="5" t="n">
@@ -34780,7 +34764,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
@@ -34912,7 +34896,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H518" s="5" t="n">
@@ -34974,7 +34958,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H519" s="5" t="n">
@@ -35036,7 +35020,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H520" s="5" t="n">
@@ -35098,7 +35082,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H521" s="5" t="n">
@@ -35155,38 +35139,30 @@
       </c>
       <c r="F522" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G522" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H522" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I522" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H522" s="5" t="n">
+        <v>12235300</v>
+      </c>
+      <c r="I522" s="5" t="n">
+        <v>25597</v>
       </c>
       <c r="J522" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K522" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L522" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K522" s="5" t="n">
+        <v>12235300</v>
+      </c>
+      <c r="L522" s="5" t="n">
+        <v>25597</v>
       </c>
       <c r="M522" s="3" t="inlineStr">
         <is>
@@ -35195,7 +35171,7 @@
       </c>
       <c r="N522" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -35440,7 +35416,7 @@
       </c>
       <c r="G526" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H526" s="5" t="n">
@@ -36240,7 +36216,7 @@
       </c>
       <c r="G538" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H538" s="5" t="n">
@@ -36302,7 +36278,7 @@
       </c>
       <c r="G539" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H539" s="5" t="n">
@@ -36364,7 +36340,7 @@
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H540" s="5" t="n">
@@ -36426,7 +36402,7 @@
       </c>
       <c r="G541" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H541" s="5" t="n">
@@ -36483,38 +36459,30 @@
       </c>
       <c r="F542" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G542" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H542" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I542" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H542" s="5" t="n">
+        <v>12120000</v>
+      </c>
+      <c r="I542" s="5" t="n">
+        <v>25356</v>
       </c>
       <c r="J542" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K542" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L542" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K542" s="5" t="n">
+        <v>12120000</v>
+      </c>
+      <c r="L542" s="5" t="n">
+        <v>25356</v>
       </c>
       <c r="M542" s="3" t="inlineStr">
         <is>
@@ -36523,7 +36491,7 @@
       </c>
       <c r="N542" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -36558,7 +36526,7 @@
       </c>
       <c r="G543" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H543" s="5" t="n">
@@ -36690,7 +36658,7 @@
       </c>
       <c r="G545" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H545" s="5" t="n">
@@ -36752,7 +36720,7 @@
       </c>
       <c r="G546" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H546" s="5" t="n">
@@ -36884,7 +36852,7 @@
       </c>
       <c r="G548" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H548" s="5" t="n">
@@ -36946,7 +36914,7 @@
       </c>
       <c r="G549" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H549" s="5" t="n">
@@ -37008,7 +36976,7 @@
       </c>
       <c r="G550" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H550" s="5" t="n">
@@ -37070,7 +37038,7 @@
       </c>
       <c r="G551" s="3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H551" s="5" t="n">
@@ -37337,38 +37305,30 @@
       </c>
       <c r="F555" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G555" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H555" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I555" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H555" s="5" t="n">
+        <v>14724000</v>
+      </c>
+      <c r="I555" s="5" t="n">
+        <v>33013</v>
       </c>
       <c r="J555" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K555" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L555" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K555" s="5" t="n">
+        <v>14724000</v>
+      </c>
+      <c r="L555" s="5" t="n">
+        <v>33013</v>
       </c>
       <c r="M555" s="3" t="inlineStr">
         <is>
@@ -37377,7 +37337,7 @@
       </c>
       <c r="N555" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -37412,7 +37372,7 @@
       </c>
       <c r="G556" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H556" s="5" t="n">
@@ -37544,7 +37504,7 @@
       </c>
       <c r="G558" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H558" s="5" t="n">
@@ -37606,7 +37566,7 @@
       </c>
       <c r="G559" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H559" s="5" t="n">
@@ -37668,7 +37628,7 @@
       </c>
       <c r="G560" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H560" s="5" t="n">
@@ -37787,38 +37747,30 @@
       </c>
       <c r="F562" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G562" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H562" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I562" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H562" s="5" t="n">
+        <v>11920000</v>
+      </c>
+      <c r="I562" s="5" t="n">
+        <v>24937</v>
       </c>
       <c r="J562" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K562" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L562" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K562" s="5" t="n">
+        <v>11920000</v>
+      </c>
+      <c r="L562" s="5" t="n">
+        <v>24937</v>
       </c>
       <c r="M562" s="3" t="inlineStr">
         <is>
@@ -37827,7 +37779,7 @@
       </c>
       <c r="N562" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -37857,38 +37809,30 @@
       </c>
       <c r="F563" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G563" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H563" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I563" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H563" s="5" t="n">
+        <v>17072000</v>
+      </c>
+      <c r="I563" s="5" t="n">
+        <v>31325</v>
       </c>
       <c r="J563" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K563" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L563" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K563" s="5" t="n">
+        <v>17072000</v>
+      </c>
+      <c r="L563" s="5" t="n">
+        <v>31325</v>
       </c>
       <c r="M563" s="3" t="inlineStr">
         <is>
@@ -37897,7 +37841,7 @@
       </c>
       <c r="N563" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -37997,38 +37941,30 @@
       </c>
       <c r="F565" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G565" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H565" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I565" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H565" s="5" t="n">
+        <v>14506000</v>
+      </c>
+      <c r="I565" s="5" t="n">
+        <v>32525</v>
       </c>
       <c r="J565" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K565" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L565" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K565" s="5" t="n">
+        <v>14506000</v>
+      </c>
+      <c r="L565" s="5" t="n">
+        <v>32525</v>
       </c>
       <c r="M565" s="3" t="inlineStr">
         <is>
@@ -38037,7 +37973,7 @@
       </c>
       <c r="N565" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38072,7 +38008,7 @@
       </c>
       <c r="G566" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H566" s="5" t="n">
@@ -38204,7 +38140,7 @@
       </c>
       <c r="G568" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H568" s="5" t="n">
@@ -38266,7 +38202,7 @@
       </c>
       <c r="G569" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H569" s="5" t="n">
@@ -38328,7 +38264,7 @@
       </c>
       <c r="G570" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H570" s="5" t="n">
@@ -38390,7 +38326,7 @@
       </c>
       <c r="G571" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H571" s="5" t="n">
@@ -38452,7 +38388,7 @@
       </c>
       <c r="G572" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H572" s="5" t="n">
@@ -38509,30 +38445,38 @@
       </c>
       <c r="F573" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G573" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="H573" s="5" t="n">
-        <v>16598000</v>
-      </c>
-      <c r="I573" s="5" t="n">
-        <v>30455</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H573" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I573" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J573" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K573" s="5" t="n">
-        <v>16598000</v>
-      </c>
-      <c r="L573" s="5" t="n">
-        <v>30455</v>
+      <c r="K573" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L573" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M573" s="3" t="inlineStr">
         <is>
@@ -38541,7 +38485,7 @@
       </c>
       <c r="N573" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38646,7 +38590,7 @@
       </c>
       <c r="G575" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="H575" s="5" t="n">
@@ -38708,7 +38652,7 @@
       </c>
       <c r="G576" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H576" s="5" t="n">
@@ -38840,7 +38784,7 @@
       </c>
       <c r="G578" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H578" s="5" t="n">
@@ -38902,7 +38846,7 @@
       </c>
       <c r="G579" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H579" s="5" t="n">
@@ -38964,7 +38908,7 @@
       </c>
       <c r="G580" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H580" s="5" t="n">
@@ -39026,7 +38970,7 @@
       </c>
       <c r="G581" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H581" s="5" t="n">
@@ -39083,7 +39027,7 @@
       </c>
       <c r="F582" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G582" s="3" t="inlineStr">
@@ -39368,7 +39312,7 @@
       </c>
       <c r="G586" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H586" s="5" t="n">
@@ -39489,27 +39433,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
           <t>133</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>135</t>
         </is>
       </c>
     </row>
@@ -39810,7 +39754,7 @@
           <t>B | 1808呎 (4+房)
 $8281万
 $45,803/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr"/>
@@ -39826,7 +39770,7 @@
           <t>C | 1511呎 (4+房)
 $5435万
 $35,970/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="Q8" s="20" t="inlineStr"/>
@@ -39883,7 +39827,7 @@
           <t>C | 1511呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="Q9" s="20" t="inlineStr"/>
@@ -39907,7 +39851,7 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>A | 2230呎 (4+房)
 招标单位
@@ -39924,7 +39868,7 @@
           <t>B | 1808呎 (4+房)
 $8112万
 $44,866/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr"/>
@@ -39940,7 +39884,7 @@
           <t>C | 1511呎 (4+房)
 $5230万
 $34,613/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="Q10" s="20" t="inlineStr"/>
@@ -39969,7 +39913,7 @@
           <t>A | 2230呎 (4+房)
 $10510万
 $47,132/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr"/>
@@ -39981,7 +39925,7 @@
           <t>B | 1808呎 (4+房)
 $8018万
 $44,345/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr"/>
@@ -39997,7 +39941,7 @@
           <t>C | 1511呎 (4+房)
 $5818万
 $38,504/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="Q11" s="20" t="inlineStr"/>
@@ -40033,7 +39977,7 @@
       <c r="D12" s="20" t="inlineStr"/>
       <c r="E12" s="20" t="inlineStr"/>
       <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="25" t="inlineStr">
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t>B | 1808呎 (4+房)
 招标单位
@@ -40049,7 +39993,7 @@
       <c r="M12" s="20" t="inlineStr"/>
       <c r="N12" s="20" t="inlineStr"/>
       <c r="O12" s="20" t="inlineStr"/>
-      <c r="P12" s="25" t="inlineStr">
+      <c r="P12" s="24" t="inlineStr">
         <is>
           <t>C | 1511呎 (4+房)
 招标单位
@@ -40083,7 +40027,7 @@
           <t>A | 2230呎 (4+房)
 $9525万
 $42,713/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr"/>
@@ -40095,7 +40039,7 @@
           <t>B | 1808呎 (4+房)
 $7512万
 $41,550/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr"/>
@@ -40111,7 +40055,7 @@
           <t>C | 1511呎 (4+房)
 $5671万
 $37,530/呎
-(25年-12月-28日)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="Q13" s="20" t="inlineStr"/>
@@ -40197,7 +40141,7 @@
           <t>A | 2230呎 (4+房)
 $9321万
 $41,797/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr"/>
@@ -40209,7 +40153,7 @@
           <t>B | 1808呎 (4+房)
 $7006万
 $38,750/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr"/>
@@ -40225,7 +40169,7 @@
           <t>C | 1511呎 (4+房)
 $6222万
 $41,176/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="Q15" s="20" t="inlineStr"/>
@@ -40254,7 +40198,7 @@
           <t>A | 2230呎 (4+房)
 $9332万
 $41,850/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr"/>
@@ -40266,7 +40210,7 @@
           <t>B | 1808呎 (4+房)
 $7239万
 $40,040/呎
-(25年-12月-28日)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
@@ -40282,7 +40226,7 @@
           <t>C | 1511呎 (4+房)
 $5553万
 $36,749/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="Q16" s="20" t="inlineStr"/>
@@ -40311,7 +40255,7 @@
           <t>A | 2230呎 (4+房)
 $9228万
 $41,381/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr"/>
@@ -40323,7 +40267,7 @@
           <t>B | 1808呎 (4+房)
 $7230万
 $39,989/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr"/>
@@ -40339,7 +40283,7 @@
           <t>C | 1511呎 (4+房)
 $5485万
 $36,299/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="Q17" s="20" t="inlineStr"/>
@@ -40380,7 +40324,7 @@
           <t>B | 1808呎 (4+房)
 $7096万
 $39,246/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr"/>
@@ -40425,7 +40369,7 @@
           <t>A | 2230呎 (4+房)
 $8977万
 $40,257/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>
@@ -40437,7 +40381,7 @@
           <t>B | 1808呎 (4+房)
 $7060万
 $39,050/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr"/>
@@ -40453,7 +40397,7 @@
           <t>C | 1511呎 (4+房)
 $5419万
 $35,863/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="Q19" s="20" t="inlineStr"/>
@@ -40482,7 +40426,7 @@
           <t>A | 2230呎 (4+房)
 $8807万
 $39,494/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr"/>
@@ -40494,7 +40438,7 @@
           <t>B | 1808呎 (4+房)
 $7380万
 $40,821/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr"/>
@@ -40510,7 +40454,7 @@
           <t>C | 1513呎 (4+房)
 $5473万
 $36,174/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="Q20" s="20" t="inlineStr"/>
@@ -40548,7 +40492,7 @@
           <t>A2 | 450呎 (2房)
 $1570万
 $34,896/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -40556,7 +40500,7 @@
           <t>A3 | 308呎 (1房)
 $979万
 $31,783/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -40573,7 +40517,7 @@
           <t>B1 | 301呎 (1房)
 $827万
 $27,461/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -40581,7 +40525,7 @@
           <t>B10 | 482呎 (2房)
 $1427万
 $29,599/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="J21" s="23" t="inlineStr">
@@ -40589,7 +40533,7 @@
           <t>B2 | 308呎 (1房)
 $814万
 $26,412/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -40605,10 +40549,10 @@
           <t>B5 | 307呎 (1房)
 $852万
 $27,747/呎
-(25年-12月-01日)</t>
-        </is>
-      </c>
-      <c r="M21" s="24" t="inlineStr">
+(25年-12月-02日)</t>
+        </is>
+      </c>
+      <c r="M21" s="25" t="inlineStr">
         <is>
           <t>B6 | 304呎 (1房)
 $938万
@@ -40648,12 +40592,12 @@
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr"/>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -40661,7 +40605,7 @@
           <t>A2 | 450呎 (2房)
 $1570万
 $34,896/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -40669,7 +40613,7 @@
           <t>A3 | 308呎 (1房)
 $978万
 $31,751/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -40686,7 +40630,7 @@
           <t>B1 | 301呎 (1房)
 $821万
 $27,276/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -40694,7 +40638,7 @@
           <t>B10 | 482呎 (2房)
 $1421万
 $29,485/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
@@ -40702,7 +40646,7 @@
           <t>B2 | 308呎 (1房)
 $807万
 $26,202/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -40718,10 +40662,10 @@
           <t>B5 | 307呎 (1房)
 $842万
 $27,417/呎
-(25年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="M22" s="24" t="inlineStr">
+(25年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="M22" s="25" t="inlineStr">
         <is>
           <t>B6 | 304呎 (1房)
 $927万
@@ -40794,7 +40738,7 @@
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr"/>
-      <c r="H23" s="24" t="inlineStr">
+      <c r="H23" s="25" t="inlineStr">
         <is>
           <t>B1 | 301呎 (1房)
 $869万
@@ -40802,7 +40746,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I23" s="24" t="inlineStr">
+      <c r="I23" s="25" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
 $1651万
@@ -40810,7 +40754,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J23" s="24" t="inlineStr">
+      <c r="J23" s="25" t="inlineStr">
         <is>
           <t>B2 | 308呎 (1房)
 $890万
@@ -40826,7 +40770,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L23" s="24" t="inlineStr">
+      <c r="L23" s="25" t="inlineStr">
         <is>
           <t>B5 | 307呎 (1房)
 $927万
@@ -40834,7 +40778,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M23" s="24" t="inlineStr">
+      <c r="M23" s="25" t="inlineStr">
         <is>
           <t>B6 | 304呎 (1房)
 $918万
@@ -40874,12 +40818,12 @@
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr"/>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$4302万
+$47,378/呎
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -40887,7 +40831,7 @@
           <t>A2 | 450呎 (2房)
 $1658万
 $36,853/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -40912,10 +40856,10 @@
           <t>B1 | 301呎 (1房)
 $810万
 $26,898/呎
-(25年-12月-22日)</t>
-        </is>
-      </c>
-      <c r="I24" s="24" t="inlineStr">
+(25年-12月-23日)</t>
+        </is>
+      </c>
+      <c r="I24" s="25" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
 $1568万
@@ -40928,7 +40872,7 @@
           <t>B2 | 308呎 (1房)
 $796万
 $25,839/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr">
@@ -40936,7 +40880,7 @@
           <t>B3 | 449呎 (2房)
 $1428万
 $31,794/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="L24" s="23" t="inlineStr">
@@ -40944,10 +40888,10 @@
           <t>B5 | 307呎 (1房)
 $826万
 $26,908/呎
-(25年-11月-27日)</t>
-        </is>
-      </c>
-      <c r="M24" s="24" t="inlineStr">
+(25年-11月-28日)</t>
+        </is>
+      </c>
+      <c r="M24" s="25" t="inlineStr">
         <is>
           <t>B6 | 304呎 (1房)
 $909万
@@ -40960,7 +40904,7 @@
           <t>B8 | 787呎 (3房)
 $2404万
 $30,544/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="O24" s="21" t="inlineStr">
@@ -41000,7 +40944,7 @@
           <t>A2 | 450呎 (2房)
 $1656万
 $36,804/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -41008,7 +40952,7 @@
           <t>A3 | 308呎 (1房)
 $1026万
 $33,320/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -41025,7 +40969,7 @@
           <t>B1 | 301呎 (1房)
 $805万
 $26,737/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -41033,7 +40977,7 @@
           <t>B10 | 482呎 (2房)
 $1427万
 $29,605/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
@@ -41041,7 +40985,7 @@
           <t>B2 | 308呎 (1房)
 $790万
 $25,652/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="K25" s="23" t="inlineStr">
@@ -41049,10 +40993,10 @@
           <t>B3 | 449呎 (2房)
 $1391万
 $30,976/呎
-(25年-12月-22日)</t>
-        </is>
-      </c>
-      <c r="L25" s="24" t="inlineStr">
+(25年-12月-23日)</t>
+        </is>
+      </c>
+      <c r="L25" s="25" t="inlineStr">
         <is>
           <t>B5 | 307呎 (1房)
 $909万
@@ -41060,7 +41004,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M25" s="24" t="inlineStr">
+      <c r="M25" s="25" t="inlineStr">
         <is>
           <t>B6 | 304呎 (1房)
 $900万
@@ -41073,7 +41017,7 @@
           <t>B8 | 787呎 (3房)
 $2405万
 $30,564/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="O25" s="21" t="inlineStr">
@@ -41113,7 +41057,7 @@
           <t>A2 | 450呎 (2房)
 $1652万
 $36,700/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -41138,7 +41082,7 @@
           <t>B1 | 301呎 (1房)
 $770万
 $25,581/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -41154,7 +41098,7 @@
           <t>B2 | 308呎 (1房)
 $787万
 $25,550/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -41165,7 +41109,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="L26" s="24" t="inlineStr">
+      <c r="L26" s="25" t="inlineStr">
         <is>
           <t>B5 | 307呎 (1房)
 $889万
@@ -41218,7 +41162,7 @@
           <t>A1 | 908呎 (4+房)
 $4094万
 $45,093/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -41226,10 +41170,10 @@
           <t>A2 | 450呎 (2房)
 $1646万
 $36,578/呎
-(26年-01月-25日)</t>
-        </is>
-      </c>
-      <c r="E27" s="24" t="inlineStr">
+(26年-01月-26日)</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
         <is>
           <t>A3 | 308呎 (1房)
 $1105万
@@ -41251,7 +41195,7 @@
           <t>B1 | 301呎 (1房)
 $766万
 $25,446/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -41259,7 +41203,7 @@
           <t>B10 | 482呎 (2房)
 $1337万
 $27,732/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
@@ -41267,7 +41211,7 @@
           <t>B2 | 308呎 (1房)
 $785万
 $25,480/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="K27" s="23" t="inlineStr">
@@ -41275,7 +41219,7 @@
           <t>B3 | 449呎 (2房)
 $1372万
 $30,557/呎
-(26年-01月-04日)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -41299,7 +41243,7 @@
           <t>B8 | 787呎 (3房)
 $2401万
 $30,508/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="O27" s="21" t="inlineStr">
@@ -41342,7 +41286,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E28" s="25" t="inlineStr">
         <is>
           <t>A3 | 308呎 (1房)
 $1088万
@@ -41359,7 +41303,7 @@
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr"/>
-      <c r="H28" s="24" t="inlineStr">
+      <c r="H28" s="25" t="inlineStr">
         <is>
           <t>B1 | 301呎 (1房)
 $849万
@@ -41375,7 +41319,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J28" s="24" t="inlineStr">
+      <c r="J28" s="25" t="inlineStr">
         <is>
           <t>B2 | 308呎 (1房)
 $869万
@@ -41439,12 +41383,12 @@
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr"/>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="25" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -41452,7 +41396,7 @@
           <t>A2 | 450呎 (2房)
 $1631万
 $36,238/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -41477,7 +41421,7 @@
           <t>B1 | 301呎 (1房)
 $762万
 $25,327/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -41485,7 +41429,7 @@
           <t>B10 | 482呎 (2房)
 $1310万
 $27,178/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
@@ -41493,7 +41437,7 @@
           <t>B2 | 308呎 (1房)
 $780万
 $25,328/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -41557,7 +41501,7 @@
           <t>A1 | 908呎 (4+房)
 $3459万
 $38,093/呎
-(26年-07月-17日)</t>
+(26年-07月-18日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -41565,7 +41509,7 @@
           <t>A2 | 450呎 (2房)
 $1595万
 $35,440/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
@@ -41573,7 +41517,7 @@
           <t>A3 | 308呎 (1房)
 $947万
 $30,732/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -41590,7 +41534,7 @@
           <t>B1 | 301呎 (1房)
 $761万
 $25,276/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
@@ -41598,7 +41542,7 @@
           <t>B10 | 482呎 (2房)
 $1282万
 $26,604/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
@@ -41606,7 +41550,7 @@
           <t>B2 | 308呎 (1房)
 $779万
 $25,277/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr">
@@ -41614,7 +41558,7 @@
           <t>B3 | 449呎 (2房)
 $1334万
 $29,711/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="L30" s="23" t="inlineStr">
@@ -41622,7 +41566,7 @@
           <t>B5 | 307呎 (1房)
 $825万
 $26,881/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -41638,7 +41582,7 @@
           <t>B8 | 787呎 (3房)
 $2312万
 $29,376/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="O30" s="21" t="inlineStr">
@@ -41681,7 +41625,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E31" s="24" t="inlineStr">
+      <c r="E31" s="25" t="inlineStr">
         <is>
           <t>A3 | 308呎 (1房)
 $1043万
@@ -41703,7 +41647,7 @@
           <t>B1 | 301呎 (1房)
 $759万
 $25,226/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -41719,7 +41663,7 @@
           <t>B2 | 308呎 (1房)
 $777万
 $25,226/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -41735,7 +41679,7 @@
           <t>B5 | 307呎 (1房)
 $825万
 $26,860/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -41751,7 +41695,7 @@
           <t>B8 | 787呎 (3房)
 $2305万
 $29,288/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="O31" s="21" t="inlineStr">
@@ -41794,7 +41738,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E32" s="25" t="inlineStr">
         <is>
           <t>A3 | 308呎 (1房)
 $1035万
@@ -41816,7 +41760,7 @@
           <t>B1 | 301呎 (1房)
 $758万
 $25,175/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
@@ -41824,7 +41768,7 @@
           <t>B10 | 482呎 (2房)
 $1278万
 $26,519/呎
-(26年-01月-27日)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
@@ -41832,7 +41776,7 @@
           <t>B2 | 308呎 (1房)
 $774万
 $25,144/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="K32" s="21" t="inlineStr">
@@ -41864,7 +41808,7 @@
           <t>B8 | 787呎 (3房)
 $2387万
 $30,326/呎
-(26年-01月-25日)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="O32" s="21" t="inlineStr">
@@ -41904,7 +41848,7 @@
           <t>A2 | 450呎 (2房)
 $1600万
 $35,556/呎
-(26年-01月-21日)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -41929,7 +41873,7 @@
           <t>B1 | 301呎 (1房)
 $756万
 $25,125/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I33" s="23" t="inlineStr">
@@ -41937,7 +41881,7 @@
           <t>B10 | 482呎 (2房)
 $1256万
 $26,063/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
@@ -41945,7 +41889,7 @@
           <t>B2 | 308呎 (1房)
 $774万
 $25,126/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr">
@@ -41953,7 +41897,7 @@
           <t>B3 | 449呎 (2房)
 $1311万
 $29,190/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="L33" s="21" t="inlineStr">
@@ -41977,7 +41921,7 @@
           <t>B8 | 787呎 (3房)
 $2258万
 $28,689/呎
-(25年-12月-28日)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="O33" s="21" t="inlineStr">
@@ -42009,7 +41953,7 @@
           <t>A1 | 908呎 (4+房)
 $3815万
 $42,014/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
@@ -42017,7 +41961,7 @@
           <t>A2 | 450呎 (2房)
 $1576万
 $35,026/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -42042,7 +41986,7 @@
           <t>B1 | 301呎 (1房)
 $753万
 $25,024/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -42058,7 +42002,7 @@
           <t>B2 | 308呎 (1房)
 $771万
 $25,025/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="K34" s="21" t="inlineStr">
@@ -42074,7 +42018,7 @@
           <t>B5 | 307呎 (1房)
 $823万
 $26,816/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="M34" s="21" t="inlineStr">
@@ -42130,7 +42074,7 @@
           <t>A2 | 450呎 (2房)
 $1526万
 $33,900/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -42155,7 +42099,7 @@
           <t>B1 | 301呎 (1房)
 $750万
 $24,924/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
@@ -42163,7 +42107,7 @@
           <t>B10 | 482呎 (2房)
 $1239万
 $25,705/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="J35" s="23" t="inlineStr">
@@ -42171,7 +42115,7 @@
           <t>B2 | 308呎 (1房)
 $768万
 $24,925/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
@@ -42179,7 +42123,7 @@
           <t>B3 | 449呎 (2房)
 $1305万
 $29,062/呎
-(26年-01月-28日)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="L35" s="23" t="inlineStr">
@@ -42187,7 +42131,7 @@
           <t>B5 | 307呎 (1房)
 $820万
 $26,708/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="M35" s="21" t="inlineStr">
@@ -42203,7 +42147,7 @@
           <t>B8 | 787呎 (3房)
 $2296万
 $29,180/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="O35" s="21" t="inlineStr">
@@ -42263,7 +42207,7 @@
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr"/>
-      <c r="H36" s="24" t="inlineStr">
+      <c r="H36" s="25" t="inlineStr">
         <is>
           <t>B1 | 301呎 (1房)
 $829万
@@ -42279,7 +42223,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J36" s="24" t="inlineStr">
+      <c r="J36" s="25" t="inlineStr">
         <is>
           <t>B2 | 308呎 (1房)
 $848万
@@ -42348,18 +42292,18 @@
           <t>A1 | 908呎 (4+房)
 $3357万
 $36,969/呎
-(26年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="D37" s="22" t="inlineStr">
+(26年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="D37" s="25" t="inlineStr">
         <is>
           <t>A2 | 450呎 (2房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E37" s="24" t="inlineStr">
+招标单位
+-
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
         <is>
           <t>A3 | 308呎 (1房)
 $1011万
@@ -42381,10 +42325,10 @@
           <t>B1 | 301呎 (1房)
 $772万
 $25,635/呎
-(25年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="I37" s="24" t="inlineStr">
+(25年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="I37" s="25" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
 $1417万
@@ -42397,7 +42341,7 @@
           <t>B2 | 308呎 (1房)
 $758万
 $24,626/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="K37" s="21" t="inlineStr">
@@ -42472,7 +42416,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E38" s="25" t="inlineStr">
         <is>
           <t>A3 | 308呎 (1房)
 $1003万
@@ -42494,7 +42438,7 @@
           <t>B1 | 301呎 (1房)
 $765万
 $25,430/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="I38" s="23" t="inlineStr">
@@ -42502,7 +42446,7 @@
           <t>B10 | 482呎 (2房)
 $1220万
 $25,315/呎
-(25年-12月-28日)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="J38" s="23" t="inlineStr">
@@ -42510,7 +42454,7 @@
           <t>B2 | 308呎 (1房)
 $752万
 $24,429/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="K38" s="21" t="inlineStr">
@@ -42542,7 +42486,7 @@
           <t>B8 | 787呎 (3房)
 $2184万
 $27,750/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="O38" s="21" t="inlineStr">
@@ -42569,7 +42513,7 @@
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr"/>
-      <c r="C39" s="25" t="inlineStr">
+      <c r="C39" s="24" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
@@ -42577,12 +42521,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D39" s="22" t="inlineStr">
+      <c r="D39" s="25" t="inlineStr">
         <is>
           <t>A2 | 450呎 (2房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
@@ -42590,7 +42534,7 @@
           <t>A3 | 308呎 (1房)
 $899万
 $29,181/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
@@ -42607,7 +42551,7 @@
           <t>B1 | 301呎 (1房)
 $758万
 $25,193/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="I39" s="23" t="inlineStr">
@@ -42615,7 +42559,7 @@
           <t>B10 | 482呎 (2房)
 $1212万
 $25,145/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="J39" s="23" t="inlineStr">
@@ -42623,7 +42567,7 @@
           <t>B2 | 308呎 (1房)
 $746万
 $24,233/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
@@ -42631,7 +42575,7 @@
           <t>B3 | 449呎 (2房)
 $1240万
 $27,627/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="L39" s="23" t="inlineStr">
@@ -42639,7 +42583,7 @@
           <t>B5 | 307呎 (1房)
 $793万
 $25,819/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="M39" s="23" t="inlineStr">
@@ -42647,7 +42591,7 @@
           <t>B6 | 304呎 (1房)
 $785万
 $25,818/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="N39" s="23" t="inlineStr">
@@ -42655,7 +42599,7 @@
           <t>B8 | 787呎 (3房)
 $2169万
 $27,555/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="O39" s="21" t="inlineStr">
@@ -42687,7 +42631,7 @@
           <t>A1 | 908呎 (4+房)
 $3354万
 $36,941/呎
-(26年-07月-17日)</t>
+(26年-07月-18日)</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -42703,7 +42647,7 @@
           <t>A3 | 308呎 (1房)
 $861万
 $27,963/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr">
@@ -42720,7 +42664,7 @@
           <t>B1 | 301呎 (1房)
 $721万
 $23,946/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="I40" s="23" t="inlineStr">
@@ -42728,7 +42672,7 @@
           <t>B10 | 482呎 (2房)
 $1210万
 $25,104/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="J40" s="23" t="inlineStr">
@@ -42736,7 +42680,7 @@
           <t>B2 | 308呎 (1房)
 $738万
 $23,946/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
@@ -42744,7 +42688,7 @@
           <t>B3 | 449呎 (2房)
 $1260万
 $28,062/呎
-(26年-02月-02日)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="L40" s="23" t="inlineStr">
@@ -42752,7 +42696,7 @@
           <t>B5 | 307呎 (1房)
 $785万
 $25,560/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="M40" s="23" t="inlineStr">
@@ -42760,7 +42704,7 @@
           <t>B6 | 304呎 (1房)
 $776万
 $25,527/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="N40" s="23" t="inlineStr">
@@ -42768,7 +42712,7 @@
           <t>B8 | 787呎 (3房)
 $2130万
 $27,062/呎
-(26年-01月-05日)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="O40" s="21" t="inlineStr">
@@ -42795,12 +42739,12 @@
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr"/>
-      <c r="C41" s="22" t="inlineStr">
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$3110万
+$34,251/呎
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
@@ -42808,7 +42752,7 @@
           <t>A2 | 450呎 (2房)
 $1214万
 $26,979/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
@@ -42816,7 +42760,7 @@
           <t>A3 | 308呎 (1房)
 $845万
 $27,432/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="F41" s="21" t="inlineStr">
@@ -42833,7 +42777,7 @@
           <t>B1 | 301呎 (1房)
 $681万
 $22,617/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="I41" s="23" t="inlineStr">
@@ -42841,7 +42785,7 @@
           <t>B10 | 482呎 (2房)
 $1198万
 $24,861/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="J41" s="23" t="inlineStr">
@@ -42849,7 +42793,7 @@
           <t>B2 | 308呎 (1房)
 $697万
 $22,618/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="K41" s="21" t="inlineStr">
@@ -42865,7 +42809,7 @@
           <t>B5 | 307呎 (1房)
 $777万
 $25,304/呎
-(25年-12月-16日)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="M41" s="23" t="inlineStr">
@@ -42873,7 +42817,7 @@
           <t>B6 | 304呎 (1房)
 $769万
 $25,304/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="N41" s="23" t="inlineStr">
@@ -42881,7 +42825,7 @@
           <t>B8 | 787呎 (3房)
 $2157万
 $27,409/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="O41" s="23" t="inlineStr">
@@ -42889,7 +42833,7 @@
           <t>B9 | 296呎 (1房)
 $730万
 $24,675/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="P41" s="20" t="inlineStr"/>
@@ -42987,7 +42931,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -42997,17 +42941,17 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>106</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>109</t>
         </is>
       </c>
     </row>
@@ -43136,7 +43080,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="Q5" s="25" t="inlineStr">
+      <c r="Q5" s="24" t="inlineStr">
         <is>
           <t>PSH B | 3553呎 (4+房)
 招标单位
@@ -43177,7 +43121,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="S6" s="25" t="inlineStr">
+      <c r="S6" s="24" t="inlineStr">
         <is>
           <t>PSV B | 2765呎 (4+房)
 招标单位
@@ -43223,7 +43167,7 @@
           <t>C | 1227呎 (4+房)
 $5225万
 $42,586/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="O7" s="21" t="inlineStr">
@@ -43245,7 +43189,7 @@
           <t>46</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>A | 1985呎 (4+房)
 招标单位
@@ -43276,7 +43220,7 @@
           <t>C | 1227呎 (4+房)
 $4824万
 $39,314/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="O8" s="22" t="inlineStr">
@@ -43356,7 +43300,7 @@
           <t>A | 1985呎 (4+房)
 $8348万
 $42,055/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr"/>
@@ -43382,7 +43326,7 @@
           <t>C | 1227呎 (4+房)
 $4330万
 $35,289/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="O10" s="23" t="inlineStr">
@@ -43390,7 +43334,7 @@
           <t>D | 1365呎 (4+房)
 $5191万
 $38,028/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="P10" s="20" t="inlineStr"/>
@@ -43443,7 +43387,7 @@
           <t>D | 1365呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="P11" s="20" t="inlineStr"/>
@@ -43457,7 +43401,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>A | 1985呎 (4+房)
 招标单位
@@ -43488,7 +43432,7 @@
           <t>C | 1227呎 (4+房)
 $4668万
 $38,044/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="O12" s="23" t="inlineStr">
@@ -43496,7 +43440,7 @@
           <t>D | 1365呎 (4+房)
 $5020万
 $36,777/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="P12" s="20" t="inlineStr"/>
@@ -43536,7 +43480,7 @@
       <c r="K13" s="20" t="inlineStr"/>
       <c r="L13" s="20" t="inlineStr"/>
       <c r="M13" s="20" t="inlineStr"/>
-      <c r="N13" s="25" t="inlineStr">
+      <c r="N13" s="24" t="inlineStr">
         <is>
           <t>C | 1227呎 (4+房)
 招标单位
@@ -43549,7 +43493,7 @@
           <t>D | 1365呎 (4+房)
 $4934万
 $36,147/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="P13" s="20" t="inlineStr"/>
@@ -43594,7 +43538,7 @@
           <t>C | 1227呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="O14" s="23" t="inlineStr">
@@ -43602,7 +43546,7 @@
           <t>D | 1365呎 (4+房)
 $4908万
 $35,956/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="P14" s="20" t="inlineStr"/>
@@ -43616,12 +43560,12 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 1985呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr"/>
@@ -43647,7 +43591,7 @@
           <t>C | 1227呎 (4+房)
 $4470万
 $36,430/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="O15" s="21" t="inlineStr">
@@ -43708,7 +43652,7 @@
           <t>D | 1365呎 (4+房)
 $4808万
 $35,223/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="P16" s="20" t="inlineStr"/>
@@ -43753,7 +43697,7 @@
           <t>C | 1227呎 (4+房)
 $4450万
 $36,267/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="O17" s="23" t="inlineStr">
@@ -43761,7 +43705,7 @@
           <t>D | 1365呎 (4+房)
 $4800万
 $35,165/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="P17" s="20" t="inlineStr"/>
@@ -43859,7 +43803,7 @@
           <t>C | 1227呎 (4+房)
 $4448万
 $36,251/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="O19" s="23" t="inlineStr">
@@ -43867,7 +43811,7 @@
           <t>D | 1365呎 (4+房)
 $4789万
 $35,084/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="P19" s="20" t="inlineStr"/>
@@ -43968,15 +43912,15 @@
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr"/>
-      <c r="H21" s="24" t="inlineStr">
+      <c r="H21" s="25" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-$1572万
-$32,888/呎
+招标单位
+-
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I21" s="24" t="inlineStr">
+      <c r="I21" s="25" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $930万
@@ -43984,7 +43928,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J21" s="24" t="inlineStr">
+      <c r="J21" s="25" t="inlineStr">
         <is>
           <t>B3 | 299呎 (1房)
 $958万
@@ -43997,7 +43941,7 @@
           <t>B5 | 299呎 (1房)
 $828万
 $27,695/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="L21" s="23" t="inlineStr">
@@ -44005,7 +43949,7 @@
           <t>B6 | 297呎 (1房)
 $826万
 $27,810/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -44035,7 +43979,7 @@
           <t>A1 | 908呎 (4+房)
 $3710万
 $40,859/呎
-(26年-01月-05日)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -44054,24 +43998,24 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="25" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr"/>
-      <c r="H22" s="25" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="I22" s="24" t="inlineStr">
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="I22" s="25" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $927万
@@ -44079,7 +44023,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J22" s="24" t="inlineStr">
+      <c r="J22" s="25" t="inlineStr">
         <is>
           <t>B3 | 299呎 (1房)
 $954万
@@ -44092,7 +44036,7 @@
           <t>B5 | 299呎 (1房)
 $859万
 $28,723/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="L22" s="23" t="inlineStr">
@@ -44100,7 +44044,7 @@
           <t>B6 | 297呎 (1房)
 $824万
 $27,732/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -44158,7 +44102,7 @@
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr"/>
-      <c r="H23" s="24" t="inlineStr">
+      <c r="H23" s="25" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 $1560万
@@ -44166,7 +44110,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I23" s="24" t="inlineStr">
+      <c r="I23" s="25" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $919万
@@ -44174,7 +44118,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J23" s="24" t="inlineStr">
+      <c r="J23" s="25" t="inlineStr">
         <is>
           <t>B3 | 299呎 (1房)
 $910万
@@ -44182,7 +44126,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K23" s="24" t="inlineStr">
+      <c r="K23" s="25" t="inlineStr">
         <is>
           <t>B5 | 299呎 (1房)
 $910万
@@ -44190,7 +44134,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L23" s="24" t="inlineStr">
+      <c r="L23" s="25" t="inlineStr">
         <is>
           <t>B6 | 297呎 (1房)
 $908万
@@ -44225,7 +44169,7 @@
           <t>A1 | 908呎 (4+房)
 $3657万
 $40,279/呎
-(25年-11月-23日)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -44233,7 +44177,7 @@
           <t>A2 | 446呎 (2房)
 $1818万
 $40,774/呎
-(26年-07月-17日)</t>
+(26年-07月-18日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -44249,7 +44193,7 @@
           <t>A5 | 545呎 (2房)
 $2071万
 $38,000/呎
-(26年-07月-17日)</t>
+(26年-07月-18日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr"/>
@@ -44258,10 +44202,10 @@
           <t>B1 | 478呎 (2房)
 $1305万
 $27,309/呎
-(26年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="I24" s="24" t="inlineStr">
+(26年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="I24" s="25" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $915万
@@ -44269,7 +44213,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J24" s="24" t="inlineStr">
+      <c r="J24" s="25" t="inlineStr">
         <is>
           <t>B3 | 299呎 (1房)
 $906万
@@ -44282,7 +44226,7 @@
           <t>B5 | 299呎 (1房)
 $816万
 $27,280/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="L24" s="23" t="inlineStr">
@@ -44290,7 +44234,7 @@
           <t>B6 | 297呎 (1房)
 $814万
 $27,394/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr">
@@ -44320,10 +44264,10 @@
           <t>A1 | 908呎 (4+房)
 $3545万
 $39,040/呎
-(25年-11月-18日)</t>
-        </is>
-      </c>
-      <c r="D25" s="25" t="inlineStr">
+(25年-11月-19日)</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
@@ -44348,15 +44292,15 @@
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr"/>
-      <c r="H25" s="24" t="inlineStr">
+      <c r="H25" s="25" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-$1540万
-$32,226/呎
+招标单位
+-
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I25" s="24" t="inlineStr">
+      <c r="I25" s="25" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $913万
@@ -44369,7 +44313,7 @@
           <t>B3 | 299呎 (1房)
 $812万
 $27,172/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="K25" s="23" t="inlineStr">
@@ -44377,7 +44321,7 @@
           <t>B5 | 299呎 (1房)
 $812万
 $27,172/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="L25" s="23" t="inlineStr">
@@ -44385,7 +44329,7 @@
           <t>B6 | 297呎 (1房)
 $810万
 $27,285/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
@@ -44415,7 +44359,7 @@
           <t>A1 | 908呎 (4+房)
 $3626万
 $39,932/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -44434,24 +44378,24 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="25" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr"/>
-      <c r="H26" s="25" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="I26" s="24" t="inlineStr">
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="I26" s="25" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $899万
@@ -44464,7 +44408,7 @@
           <t>B3 | 299呎 (1房)
 $800万
 $26,772/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr">
@@ -44472,7 +44416,7 @@
           <t>B5 | 299呎 (1房)
 $800万
 $26,772/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="L26" s="23" t="inlineStr">
@@ -44480,7 +44424,7 @@
           <t>B6 | 297呎 (1房)
 $798万
 $26,884/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr">
@@ -44510,15 +44454,15 @@
           <t>A1 | 908呎 (4+房)
 $3605万
 $39,705/呎
-(25年-11月-23日)</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
+(25年-11月-24日)</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1688万
+$37,848/呎
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -44534,7 +44478,7 @@
           <t>A5 | 545呎 (2房)
 $2015万
 $36,978/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr"/>
@@ -44543,7 +44487,7 @@
           <t>B1 | 478呎 (2房)
 $1253万
 $26,218/呎
-(26年-07月-18日)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -44567,7 +44511,7 @@
           <t>B5 | 299呎 (1房)
 $790万
 $26,428/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="L27" s="23" t="inlineStr">
@@ -44575,7 +44519,7 @@
           <t>B6 | 297呎 (1房)
 $818万
 $27,551/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -44657,7 +44601,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="K28" s="24" t="inlineStr">
+      <c r="K28" s="25" t="inlineStr">
         <is>
           <t>B5 | 299呎 (1房)
 $868万
@@ -44665,7 +44609,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L28" s="24" t="inlineStr">
+      <c r="L28" s="25" t="inlineStr">
         <is>
           <t>B6 | 297呎 (1房)
 $898万
@@ -44700,10 +44644,10 @@
           <t>A1 | 908呎 (4+房)
 $3501万
 $38,558/呎
-(25年-11月-27日)</t>
-        </is>
-      </c>
-      <c r="D29" s="25" t="inlineStr">
+(25年-11月-28日)</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
@@ -44728,12 +44672,12 @@
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr"/>
-      <c r="H29" s="25" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -44757,7 +44701,7 @@
           <t>B5 | 299呎 (1房)
 $768万
 $25,670/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="L29" s="23" t="inlineStr">
@@ -44765,7 +44709,7 @@
           <t>B6 | 297呎 (1房)
 $795万
 $26,760/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
@@ -44795,7 +44739,7 @@
           <t>A1 | 908呎 (4+房)
 $3335万
 $36,730/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -44803,7 +44747,7 @@
           <t>A2 | 446呎 (2房)
 $1690万
 $37,892/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -44819,7 +44763,7 @@
           <t>A5 | 545呎 (2房)
 $1962万
 $36,000/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr"/>
@@ -44828,7 +44772,7 @@
           <t>B1 | 478呎 (2房)
 $1243万
 $26,000/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -44852,7 +44796,7 @@
           <t>B5 | 299呎 (1房)
 $766万
 $25,618/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="L30" s="23" t="inlineStr">
@@ -44860,7 +44804,7 @@
           <t>B6 | 297呎 (1房)
 $793万
 $26,706/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -44918,12 +44862,12 @@
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr"/>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="H31" s="25" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -44947,7 +44891,7 @@
           <t>B5 | 299呎 (1房)
 $764万
 $25,567/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="L31" s="23" t="inlineStr">
@@ -44955,7 +44899,7 @@
           <t>B6 | 297呎 (1房)
 $791万
 $26,620/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -44985,10 +44929,10 @@
           <t>A1 | 908呎 (4+房)
 $3557万
 $39,172/呎
-(25年-11月-27日)</t>
-        </is>
-      </c>
-      <c r="D32" s="25" t="inlineStr">
+(25年-11月-28日)</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
@@ -45021,7 +44965,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I32" s="24" t="inlineStr">
+      <c r="I32" s="25" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $890万
@@ -45034,7 +44978,7 @@
           <t>B3 | 299呎 (1房)
 $792万
 $26,489/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
@@ -45042,7 +44986,7 @@
           <t>B5 | 299呎 (1房)
 $763万
 $25,516/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="L32" s="23" t="inlineStr">
@@ -45050,7 +44994,7 @@
           <t>B6 | 297呎 (1房)
 $789万
 $26,566/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr">
@@ -45121,7 +45065,7 @@
           <t>B2 | 302呎 (1房)
 $799万
 $26,470/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
@@ -45129,7 +45073,7 @@
           <t>B3 | 299呎 (1房)
 $789万
 $26,403/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr">
@@ -45137,7 +45081,7 @@
           <t>B5 | 299呎 (1房)
 $790万
 $26,436/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="L33" s="23" t="inlineStr">
@@ -45145,7 +45089,7 @@
           <t>B6 | 297呎 (1房)
 $787万
 $26,513/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="M33" s="21" t="inlineStr">
@@ -45175,7 +45119,7 @@
           <t>A1 | 908呎 (4+房)
 $3610万
 $39,758/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
@@ -45183,7 +45127,7 @@
           <t>A2 | 446呎 (2房)
 $1552万
 $34,807/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -45194,12 +45138,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="23" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1900万
+$34,859/呎
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr"/>
@@ -45208,7 +45152,7 @@
           <t>B1 | 478呎 (2房)
 $1207万
 $25,251/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="I34" s="23" t="inlineStr">
@@ -45216,7 +45160,7 @@
           <t>B2 | 302呎 (1房)
 $796万
 $26,364/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="J34" s="23" t="inlineStr">
@@ -45224,7 +45168,7 @@
           <t>B3 | 299呎 (1房)
 $787万
 $26,330/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr">
@@ -45232,7 +45176,7 @@
           <t>B5 | 299呎 (1房)
 $787万
 $26,330/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="L34" s="23" t="inlineStr">
@@ -45240,7 +45184,7 @@
           <t>B6 | 297呎 (1房)
 $785万
 $26,440/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="M34" s="21" t="inlineStr">
@@ -45270,7 +45214,7 @@
           <t>A1 | 908呎 (4+房)
 $3366万
 $37,070/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
@@ -45298,12 +45242,12 @@
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr"/>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H35" s="23" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1224万
+$25,597/呎
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
@@ -45311,7 +45255,7 @@
           <t>B2 | 302呎 (1房)
 $792万
 $26,225/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="J35" s="23" t="inlineStr">
@@ -45319,7 +45263,7 @@
           <t>B3 | 299呎 (1房)
 $784万
 $26,225/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
@@ -45327,7 +45271,7 @@
           <t>B5 | 299呎 (1房)
 $783万
 $26,192/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="L35" s="23" t="inlineStr">
@@ -45335,7 +45279,7 @@
           <t>B6 | 297呎 (1房)
 $782万
 $26,334/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="M35" s="21" t="inlineStr">
@@ -45401,7 +45345,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I36" s="24" t="inlineStr">
+      <c r="I36" s="25" t="inlineStr">
         <is>
           <t>B2 | 302呎 (1房)
 $875万
@@ -45409,7 +45353,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J36" s="24" t="inlineStr">
+      <c r="J36" s="25" t="inlineStr">
         <is>
           <t>B3 | 299呎 (1房)
 $866万
@@ -45417,7 +45361,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K36" s="24" t="inlineStr">
+      <c r="K36" s="25" t="inlineStr">
         <is>
           <t>B5 | 299呎 (1房)
 $866万
@@ -45425,7 +45369,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L36" s="24" t="inlineStr">
+      <c r="L36" s="25" t="inlineStr">
         <is>
           <t>B6 | 297呎 (1房)
 $864万
@@ -45460,7 +45404,7 @@
           <t>A1 | 908呎 (4+房)
 $3136万
 $34,543/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
@@ -45468,7 +45412,7 @@
           <t>A2 | 446呎 (2房)
 $1469万
 $32,937/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -45484,16 +45428,16 @@
           <t>A5 | 545呎 (2房)
 $1738万
 $31,888/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr"/>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="H37" s="23" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1212万
+$25,356/呎
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="I37" s="23" t="inlineStr">
@@ -45501,7 +45445,7 @@
           <t>B2 | 302呎 (1房)
 $782万
 $25,878/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="J37" s="23" t="inlineStr">
@@ -45509,7 +45453,7 @@
           <t>B3 | 299呎 (1房)
 $775万
 $25,911/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="K37" s="23" t="inlineStr">
@@ -45517,7 +45461,7 @@
           <t>B5 | 299呎 (1房)
 $775万
 $25,911/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="L37" s="23" t="inlineStr">
@@ -45525,7 +45469,7 @@
           <t>B6 | 297呎 (1房)
 $773万
 $26,019/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="M37" s="21" t="inlineStr">
@@ -45555,15 +45499,15 @@
           <t>A1 | 908呎 (4+房)
 $3033万
 $33,401/呎
-(25年-11月-05日)</t>
-        </is>
-      </c>
-      <c r="D38" s="22" t="inlineStr">
+(25年-11月-06日)</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1472万
+$33,013/呎
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -45596,7 +45540,7 @@
           <t>B2 | 302呎 (1房)
 $776万
 $25,704/呎
-(25年-12月-22日)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="J38" s="23" t="inlineStr">
@@ -45604,7 +45548,7 @@
           <t>B3 | 299呎 (1房)
 $769万
 $25,703/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
@@ -45612,7 +45556,7 @@
           <t>B5 | 299呎 (1房)
 $769万
 $25,703/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="L38" s="23" t="inlineStr">
@@ -45620,7 +45564,7 @@
           <t>B6 | 297呎 (1房)
 $767万
 $25,810/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="M38" s="21" t="inlineStr">
@@ -45650,15 +45594,15 @@
           <t>A1 | 908呎 (4+房)
 $3064万
 $33,745/呎
-(25年-11月-13日)</t>
-        </is>
-      </c>
-      <c r="D39" s="22" t="inlineStr">
+(25年-11月-14日)</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1451万
+$32,525/呎
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
@@ -45669,21 +45613,21 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F39" s="22" t="inlineStr">
+      <c r="F39" s="23" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1707万
+$31,325/呎
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr"/>
-      <c r="H39" s="22" t="inlineStr">
+      <c r="H39" s="23" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1192万
+$24,937/呎
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="I39" s="22" t="inlineStr">
@@ -45699,7 +45643,7 @@
           <t>B3 | 299呎 (1房)
 $745万
 $24,902/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
@@ -45707,7 +45651,7 @@
           <t>B5 | 299呎 (1房)
 $718万
 $23,998/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="L39" s="23" t="inlineStr">
@@ -45715,7 +45659,7 @@
           <t>B6 | 297呎 (1房)
 $716万
 $24,098/呎
-(25年-12月-16日)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="M39" s="21" t="inlineStr">
@@ -45745,7 +45689,7 @@
           <t>A1 | 908呎 (4+房)
 $3012万
 $33,172/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
@@ -45753,7 +45697,7 @@
           <t>A2 | 446呎 (2房)
 $1423万
 $31,901/呎
-(26年-07月-17日)</t>
+(26年-07月-18日)</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
@@ -45764,12 +45708,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F40" s="23" t="inlineStr">
+      <c r="F40" s="22" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
-$1660万
-$30,455/呎
-(26年-07月-17日)</t>
+招标单位
+-
+(暂停销售)</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr"/>
@@ -45778,7 +45722,7 @@
           <t>B1 | 478呎 (2房)
 $1178万
 $24,644/呎
-(26年-07月-18日)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="I40" s="23" t="inlineStr">
@@ -45786,7 +45730,7 @@
           <t>B2 | 302呎 (1房)
 $746万
 $24,686/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="J40" s="23" t="inlineStr">
@@ -45794,7 +45738,7 @@
           <t>B3 | 299呎 (1房)
 $738万
 $24,685/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
@@ -45802,7 +45746,7 @@
           <t>B5 | 299呎 (1房)
 $710万
 $23,758/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="L40" s="23" t="inlineStr">
@@ -45810,7 +45754,7 @@
           <t>B6 | 297呎 (1房)
 $709万
 $23,857/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="M40" s="21" t="inlineStr">
@@ -45840,10 +45784,10 @@
           <t>A1 | 874呎 (4+房)
 $2659万
 $30,427/呎
-(25年-12月-17日)</t>
-        </is>
-      </c>
-      <c r="D41" s="25" t="inlineStr">
+(25年-12月-18日)</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
@@ -45859,7 +45803,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F41" s="25" t="inlineStr">
+      <c r="F41" s="24" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
@@ -45868,12 +45812,12 @@
         </is>
       </c>
       <c r="G41" s="20" t="inlineStr"/>
-      <c r="H41" s="25" t="inlineStr">
+      <c r="H41" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="I41" s="23" t="inlineStr">
@@ -45881,7 +45825,7 @@
           <t>B2 | 302呎 (1房)
 $719万
 $23,809/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="J41" s="23" t="inlineStr">
@@ -45889,7 +45833,7 @@
           <t>B3 | 299呎 (1房)
 $712万
 $23,808/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
@@ -45897,7 +45841,7 @@
           <t>B5 | 299呎 (1房)
 $685万
 $22,923/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="L41" s="23" t="inlineStr">
@@ -45905,7 +45849,7 @@
           <t>B6 | 297呎 (1房)
 $683万
 $22,985/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="M41" s="21" t="inlineStr">

--- a/web/files/九龙-启德-天玺．天第2期.xlsx
+++ b/web/files/九龙-启德-天玺．天第2期.xlsx
@@ -23591,7 +23591,7 @@
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
@@ -23601,12 +23601,12 @@
       </c>
       <c r="H348" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I348" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J348" s="3" t="inlineStr">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L348" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M348" s="3" t="inlineStr">
@@ -23631,7 +23631,7 @@
       </c>
       <c r="N348" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -24407,7 +24407,7 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -24417,12 +24417,12 @@
       </c>
       <c r="H360" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I360" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J360" s="3" t="inlineStr">
@@ -24432,12 +24432,12 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L360" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M360" s="3" t="inlineStr">
@@ -24447,7 +24447,7 @@
       </c>
       <c r="N360" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -42936,7 +42936,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -42951,7 +42951,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>107</t>
         </is>
       </c>
     </row>
@@ -43454,12 +43454,12 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>A | 1985呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr"/>
@@ -43613,12 +43613,12 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>A | 1985呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr"/>

--- a/web/files/九龙-启德-天玺．天第2期.xlsx
+++ b/web/files/九龙-启德-天玺．天第2期.xlsx
@@ -24135,38 +24135,30 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H356" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I356" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H356" s="5" t="n">
+        <v>82430000</v>
+      </c>
+      <c r="I356" s="5" t="n">
+        <v>41526</v>
       </c>
       <c r="J356" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K356" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L356" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K356" s="5" t="n">
+        <v>82430000</v>
+      </c>
+      <c r="L356" s="5" t="n">
+        <v>41526</v>
       </c>
       <c r="M356" s="3" t="inlineStr">
         <is>
@@ -24175,7 +24167,7 @@
       </c>
       <c r="N356" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -32049,30 +32041,38 @@
       </c>
       <c r="F475" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="H475" s="5" t="n">
-        <v>16900000</v>
-      </c>
-      <c r="I475" s="5" t="n">
-        <v>37892</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H475" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I475" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J475" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K475" s="5" t="n">
-        <v>16900000</v>
-      </c>
-      <c r="L475" s="5" t="n">
-        <v>37892</v>
+      <c r="K475" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L475" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M475" s="3" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
       </c>
       <c r="N475" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -34697,30 +34697,38 @@
       </c>
       <c r="F515" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="H515" s="5" t="n">
-        <v>15524000</v>
-      </c>
-      <c r="I515" s="5" t="n">
-        <v>34807</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H515" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I515" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J515" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K515" s="5" t="n">
-        <v>15524000</v>
-      </c>
-      <c r="L515" s="5" t="n">
-        <v>34807</v>
+      <c r="K515" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L515" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M515" s="3" t="inlineStr">
         <is>
@@ -34729,7 +34737,7 @@
       </c>
       <c r="N515" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -42941,12 +42949,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -43560,12 +43568,12 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 1985呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$8243万
+$41,526/呎
+(26年-07月-31日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr"/>
@@ -44742,12 +44750,12 @@
 (25年-11月-04日)</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
-$1690万
-$37,892/呎
-(26年-07月-23日)</t>
+招标单位
+-
+(暂停销售)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -45122,12 +45130,12 @@
 (25年-11月-12日)</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
-$1552万
-$34,807/呎
-(26年-07月-23日)</t>
+招标单位
+-
+(暂停销售)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">

--- a/web/files/九龙-启德-天玺．天第2期.xlsx
+++ b/web/files/九龙-启德-天玺．天第2期.xlsx
@@ -6415,7 +6415,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -12732,7 +12732,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -19895,7 +19895,7 @@
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -23591,7 +23591,7 @@
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -25875,7 +25875,7 @@
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G382" s="3" t="inlineStr">
@@ -26613,7 +26613,7 @@
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
@@ -28499,7 +28499,7 @@
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
@@ -29229,7 +29229,7 @@
       </c>
       <c r="F433" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G433" s="3" t="inlineStr">
@@ -32507,7 +32507,7 @@
       </c>
       <c r="F482" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G482" s="3" t="inlineStr">
@@ -39441,12 +39441,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -39456,7 +39456,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -40600,12 +40600,12 @@
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr"/>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -41391,12 +41391,12 @@
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr"/>
-      <c r="C29" s="25" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -41509,7 +41509,7 @@
           <t>A1 | 908呎 (4+房)
 $3459万
 $38,093/呎
-(26年-07月-18日)</t>
+(26年-08月-03日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -42303,12 +42303,12 @@
 (26年-07月-23日)</t>
         </is>
       </c>
-      <c r="D37" s="25" t="inlineStr">
+      <c r="D37" s="24" t="inlineStr">
         <is>
           <t>A2 | 450呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E37" s="25" t="inlineStr">
@@ -42521,20 +42521,20 @@
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr"/>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="22" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="D39" s="25" t="inlineStr">
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
         <is>
           <t>A2 | 450呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
@@ -42939,12 +42939,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -43462,12 +43462,12 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>A | 1985呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr"/>
@@ -43621,12 +43621,12 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>A | 1985呎 (4+房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr"/>
@@ -43920,12 +43920,12 @@
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr"/>
-      <c r="H21" s="25" t="inlineStr">
+      <c r="H21" s="24" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I21" s="25" t="inlineStr">
@@ -44006,12 +44006,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F22" s="25" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr"/>
@@ -44300,12 +44300,12 @@
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr"/>
-      <c r="H25" s="25" t="inlineStr">
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I25" s="25" t="inlineStr">
@@ -44386,12 +44386,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F26" s="25" t="inlineStr">
+      <c r="F26" s="24" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr"/>
@@ -44870,12 +44870,12 @@
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr"/>
-      <c r="H31" s="25" t="inlineStr">
+      <c r="H31" s="24" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">

--- a/web/files/九龙-启德-天玺．天第2期.xlsx
+++ b/web/files/九龙-启德-天玺．天第2期.xlsx
@@ -6221,7 +6221,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J133" s="3" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L133" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M133" s="3" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="N133" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13519,38 +13519,30 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H196" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I196" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="H196" s="5" t="n">
+        <v>35542000</v>
+      </c>
+      <c r="I196" s="5" t="n">
+        <v>39143</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K196" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L196" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K196" s="5" t="n">
+        <v>35542000</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>39143</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
@@ -13559,7 +13551,7 @@
       </c>
       <c r="N196" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -25875,7 +25867,7 @@
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G382" s="3" t="inlineStr">
@@ -26543,7 +26535,7 @@
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
@@ -27203,7 +27195,7 @@
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
@@ -27211,31 +27203,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H402" s="5" t="n">
-        <v>15603700</v>
-      </c>
-      <c r="I402" s="5" t="n">
-        <v>32644</v>
+      <c r="H402" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I402" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="K402" s="5" t="n">
-        <v>15135589</v>
-      </c>
-      <c r="L402" s="5" t="n">
-        <v>31664</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K402" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L402" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M402" s="3" t="inlineStr">
         <is>
-          <t>360日付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N402" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -27930,7 +27930,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -28062,7 +28062,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -28499,7 +28499,7 @@
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
@@ -28569,38 +28569,30 @@
       </c>
       <c r="F423" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H423" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I423" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="H423" s="5" t="n">
+        <v>20380000</v>
+      </c>
+      <c r="I423" s="5" t="n">
+        <v>37394</v>
       </c>
       <c r="J423" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K423" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L423" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K423" s="5" t="n">
+        <v>20380000</v>
+      </c>
+      <c r="L423" s="5" t="n">
+        <v>37394</v>
       </c>
       <c r="M423" s="3" t="inlineStr">
         <is>
@@ -28609,7 +28601,7 @@
       </c>
       <c r="N423" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -29159,7 +29151,7 @@
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
@@ -29229,7 +29221,7 @@
       </c>
       <c r="F433" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G433" s="3" t="inlineStr">
@@ -29840,7 +29832,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -30487,7 +30479,7 @@
       </c>
       <c r="F452" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G452" s="3" t="inlineStr">
@@ -30497,12 +30489,12 @@
       </c>
       <c r="H452" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I452" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J452" s="3" t="inlineStr">
@@ -30512,12 +30504,12 @@
       </c>
       <c r="K452" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L452" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M452" s="3" t="inlineStr">
@@ -30527,7 +30519,7 @@
       </c>
       <c r="N452" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -31171,38 +31163,30 @@
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H462" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I462" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="H462" s="5" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="I462" s="5" t="n">
+        <v>26151</v>
       </c>
       <c r="J462" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K462" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L462" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K462" s="5" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="L462" s="5" t="n">
+        <v>26151</v>
       </c>
       <c r="M462" s="3" t="inlineStr">
         <is>
@@ -31211,7 +31195,7 @@
       </c>
       <c r="N462" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -31914,7 +31898,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -32507,7 +32491,7 @@
       </c>
       <c r="F482" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G482" s="3" t="inlineStr">
@@ -32577,7 +32561,7 @@
       </c>
       <c r="F483" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G483" s="3" t="inlineStr">
@@ -32587,12 +32571,12 @@
       </c>
       <c r="H483" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I483" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J483" s="3" t="inlineStr">
@@ -32602,12 +32586,12 @@
       </c>
       <c r="K483" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L483" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M483" s="3" t="inlineStr">
@@ -32617,7 +32601,7 @@
       </c>
       <c r="N483" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -32787,7 +32771,7 @@
       </c>
       <c r="F486" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G486" s="3" t="inlineStr">
@@ -33175,7 +33159,7 @@
       </c>
       <c r="F492" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G492" s="3" t="inlineStr">
@@ -33185,12 +33169,12 @@
       </c>
       <c r="H492" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I492" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J492" s="3" t="inlineStr">
@@ -33200,12 +33184,12 @@
       </c>
       <c r="K492" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L492" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M492" s="3" t="inlineStr">
@@ -33215,7 +33199,7 @@
       </c>
       <c r="N492" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -33835,7 +33819,7 @@
       </c>
       <c r="F502" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G502" s="3" t="inlineStr">
@@ -33845,12 +33829,12 @@
       </c>
       <c r="H502" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I502" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J502" s="3" t="inlineStr">
@@ -33860,12 +33844,12 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M502" s="3" t="inlineStr">
@@ -33875,7 +33859,7 @@
       </c>
       <c r="N502" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -33905,38 +33889,30 @@
       </c>
       <c r="F503" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H503" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I503" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="H503" s="5" t="n">
+        <v>19729000</v>
+      </c>
+      <c r="I503" s="5" t="n">
+        <v>36200</v>
       </c>
       <c r="J503" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K503" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L503" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K503" s="5" t="n">
+        <v>19729000</v>
+      </c>
+      <c r="L503" s="5" t="n">
+        <v>36200</v>
       </c>
       <c r="M503" s="3" t="inlineStr">
         <is>
@@ -33945,7 +33921,7 @@
       </c>
       <c r="N503" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -34115,7 +34091,7 @@
       </c>
       <c r="F506" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G506" s="3" t="inlineStr">
@@ -34125,12 +34101,12 @@
       </c>
       <c r="H506" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I506" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J506" s="3" t="inlineStr">
@@ -34140,12 +34116,12 @@
       </c>
       <c r="K506" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L506" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M506" s="3" t="inlineStr">
@@ -34155,7 +34131,7 @@
       </c>
       <c r="N506" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -35799,7 +35775,7 @@
       </c>
       <c r="F532" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G532" s="3" t="inlineStr">
@@ -35809,12 +35785,12 @@
       </c>
       <c r="H532" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I532" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J532" s="3" t="inlineStr">
@@ -35824,12 +35800,12 @@
       </c>
       <c r="K532" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L532" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M532" s="3" t="inlineStr">
@@ -35839,7 +35815,7 @@
       </c>
       <c r="N532" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -36009,38 +35985,30 @@
       </c>
       <c r="F535" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G535" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H535" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I535" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="H535" s="5" t="n">
+        <v>15083000</v>
+      </c>
+      <c r="I535" s="5" t="n">
+        <v>33818</v>
       </c>
       <c r="J535" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K535" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L535" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K535" s="5" t="n">
+        <v>15083000</v>
+      </c>
+      <c r="L535" s="5" t="n">
+        <v>33818</v>
       </c>
       <c r="M535" s="3" t="inlineStr">
         <is>
@@ -36049,7 +36017,7 @@
       </c>
       <c r="N535" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -36079,7 +36047,7 @@
       </c>
       <c r="F536" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G536" s="3" t="inlineStr">
@@ -37103,38 +37071,30 @@
       </c>
       <c r="F552" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G552" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H552" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I552" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="H552" s="5" t="n">
+        <v>12091000</v>
+      </c>
+      <c r="I552" s="5" t="n">
+        <v>25295</v>
       </c>
       <c r="J552" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K552" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L552" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K552" s="5" t="n">
+        <v>12091000</v>
+      </c>
+      <c r="L552" s="5" t="n">
+        <v>25295</v>
       </c>
       <c r="M552" s="3" t="inlineStr">
         <is>
@@ -37143,7 +37103,7 @@
       </c>
       <c r="N552" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39035,38 +38995,30 @@
       </c>
       <c r="F582" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G582" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H582" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I582" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="H582" s="5" t="n">
+        <v>11702000</v>
+      </c>
+      <c r="I582" s="5" t="n">
+        <v>24481</v>
       </c>
       <c r="J582" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K582" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L582" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K582" s="5" t="n">
+        <v>11702000</v>
+      </c>
+      <c r="L582" s="5" t="n">
+        <v>24481</v>
       </c>
       <c r="M582" s="3" t="inlineStr">
         <is>
@@ -39075,7 +39027,7 @@
       </c>
       <c r="N582" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39451,17 +39403,17 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>131</t>
         </is>
       </c>
     </row>
@@ -40624,12 +40576,12 @@
 (25年-11月-28日)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>A5 | 612呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(暂停销售)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr"/>
@@ -41076,12 +41028,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>A5 | 612呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(暂停销售)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr"/>
@@ -41617,12 +41569,12 @@
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr"/>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$3554万
+$39,143/呎
+(26年-08月-06日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -42944,22 +42896,22 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>111</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -43920,12 +43872,12 @@
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr"/>
-      <c r="H21" s="24" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="I21" s="25" t="inlineStr">
@@ -44015,12 +43967,12 @@
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr"/>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="25" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(暂停销售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="I22" s="25" t="inlineStr">
@@ -44110,12 +44062,12 @@
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr"/>
-      <c r="H23" s="25" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-$1560万
-$32,644/呎
-(已定价未售)</t>
+招标单位
+-
+(暂停销售)</t>
         </is>
       </c>
       <c r="I23" s="25" t="inlineStr">
@@ -44185,7 +44137,7 @@
           <t>A2 | 446呎 (2房)
 $1818万
 $40,774/呎
-(26年-07月-18日)</t>
+(26年-08月-06日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -44201,7 +44153,7 @@
           <t>A5 | 545呎 (2房)
 $2071万
 $38,000/呎
-(26年-07月-18日)</t>
+(26年-08月-07日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr"/>
@@ -44291,21 +44243,21 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$2038万
+$37,394/呎
+(26年-08月-06日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr"/>
-      <c r="H25" s="24" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="I25" s="25" t="inlineStr">
@@ -44386,21 +44338,21 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F26" s="24" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr"/>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="25" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(暂停销售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="I26" s="25" t="inlineStr">
@@ -44495,7 +44447,7 @@
           <t>B1 | 478呎 (2房)
 $1253万
 $26,218/呎
-(26年-07月-19日)</t>
+(26年-08月-07日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -44585,12 +44537,12 @@
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr"/>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(暂停销售)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -44680,12 +44632,12 @@
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr"/>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="23" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1250万
+$26,151/呎
+(26年-08月-06日)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -44771,7 +44723,7 @@
           <t>A5 | 545呎 (2房)
 $1962万
 $36,000/呎
-(26年-07月-23日)</t>
+(26年-08月-10日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr"/>
@@ -44837,12 +44789,12 @@
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr"/>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -44861,21 +44813,21 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="24" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr"/>
-      <c r="H31" s="24" t="inlineStr">
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -44965,12 +44917,12 @@
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr"/>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="H32" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(暂停销售)</t>
         </is>
       </c>
       <c r="I32" s="25" t="inlineStr">
@@ -45027,45 +44979,45 @@
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr"/>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
+$1973万
+$36,200/呎
+(26年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr"/>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
 招标单位
 -
 (暂停销售)</t>
-        </is>
-      </c>
-      <c r="G33" s="20" t="inlineStr"/>
-      <c r="H33" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
--
--
-(待售)</t>
         </is>
       </c>
       <c r="I33" s="23" t="inlineStr">
@@ -45312,45 +45264,45 @@
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr"/>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>A2 | 446呎 (2房)
+$1508万
+$33,818/呎
+(26年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 545呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr"/>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 478呎 (2房)
+招标单位
+-
 (暂停销售)</t>
-        </is>
-      </c>
-      <c r="D36" s="22" t="inlineStr">
-        <is>
-          <t>A2 | 446呎 (2房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F36" s="21" t="inlineStr">
-        <is>
-          <t>A5 | 545呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G36" s="20" t="inlineStr"/>
-      <c r="H36" s="21" t="inlineStr">
-        <is>
-          <t>B1 | 478呎 (2房)
--
--
-(待售)</t>
         </is>
       </c>
       <c r="I36" s="25" t="inlineStr">
@@ -45535,12 +45487,12 @@
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr"/>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="H38" s="23" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1209万
+$25,295/呎
+(26年-08月-06日)</t>
         </is>
       </c>
       <c r="I38" s="23" t="inlineStr">
@@ -45820,12 +45772,12 @@
         </is>
       </c>
       <c r="G41" s="20" t="inlineStr"/>
-      <c r="H41" s="22" t="inlineStr">
+      <c r="H41" s="23" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1170万
+$24,481/呎
+(26年-08月-06日)</t>
         </is>
       </c>
       <c r="I41" s="23" t="inlineStr">

--- a/web/files/九龙-启德-天玺．天第2期.xlsx
+++ b/web/files/九龙-启德-天玺．天第2期.xlsx
@@ -26535,7 +26535,7 @@
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
@@ -29151,7 +29151,7 @@
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
@@ -43967,12 +43967,12 @@
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr"/>
-      <c r="H22" s="25" t="inlineStr">
+      <c r="H22" s="24" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I22" s="25" t="inlineStr">
@@ -44347,12 +44347,12 @@
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr"/>
-      <c r="H26" s="25" t="inlineStr">
+      <c r="H26" s="24" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I26" s="25" t="inlineStr">

--- a/web/files/九龙-启德-天玺．天第2期.xlsx
+++ b/web/files/九龙-启德-天玺．天第2期.xlsx
@@ -9551,38 +9551,30 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I136" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>41929000</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>46177</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K136" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L136" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K136" s="5" t="n">
+        <v>41929000</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>46177</v>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
@@ -9591,7 +9583,7 @@
       </c>
       <c r="N136" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -15916,7 +15908,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -17511,38 +17503,30 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H256" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I256" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H256" s="5" t="n">
+        <v>36680000</v>
+      </c>
+      <c r="I256" s="5" t="n">
+        <v>40396</v>
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K256" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L256" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K256" s="5" t="n">
+        <v>36680000</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>40396</v>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
@@ -17551,7 +17535,7 @@
       </c>
       <c r="N256" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18233,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -20660,7 +20644,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -31225,38 +31209,30 @@
       </c>
       <c r="F463" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H463" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I463" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H463" s="5" t="n">
+        <v>20211500</v>
+      </c>
+      <c r="I463" s="5" t="n">
+        <v>37085</v>
       </c>
       <c r="J463" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K463" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L463" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K463" s="5" t="n">
+        <v>20211500</v>
+      </c>
+      <c r="L463" s="5" t="n">
+        <v>37085</v>
       </c>
       <c r="M463" s="3" t="inlineStr">
         <is>
@@ -31265,7 +31241,7 @@
       </c>
       <c r="N463" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -33369,7 +33345,7 @@
       </c>
       <c r="F495" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G495" s="3" t="inlineStr">
@@ -34484,7 +34460,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H512" s="5" t="n">
@@ -39393,7 +39369,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39403,12 +39379,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>138</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -41004,12 +40980,12 @@
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr"/>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$4193万
+$46,177/呎
+(26年-08月-11日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -41913,7 +41889,7 @@
           <t>A1 | 908呎 (4+房)
 $3815万
 $42,014/呎
-(26年-07月-23日)</t>
+(26年-08月-11日)</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
@@ -42134,12 +42110,12 @@
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr"/>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$3668万
+$40,396/呎
+(26年-08月-10日)</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -42255,12 +42231,12 @@
 (26年-07月-23日)</t>
         </is>
       </c>
-      <c r="D37" s="24" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>A2 | 450呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E37" s="25" t="inlineStr">
@@ -42591,7 +42567,7 @@
           <t>A1 | 908呎 (4+房)
 $3354万
 $36,941/呎
-(26年-07月-18日)</t>
+(26年-08月-10日)</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -42891,17 +42867,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -44623,12 +44599,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$2021万
+$37,085/呎
+(26年-08月-11日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr"/>
@@ -44892,12 +44868,12 @@
 (25年-11月-28日)</t>
         </is>
       </c>
-      <c r="D32" s="24" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -45112,7 +45088,7 @@
           <t>B1 | 478呎 (2房)
 $1207万
 $25,251/呎
-(26年-07月-23日)</t>
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="I34" s="23" t="inlineStr">

--- a/web/files/九龙-启德-天玺．天第2期.xlsx
+++ b/web/files/九龙-启德-天玺．天第2期.xlsx
@@ -24375,7 +24375,7 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -26519,7 +26519,7 @@
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
@@ -42867,22 +42867,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -43549,12 +43549,12 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 1985呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr"/>
@@ -43943,12 +43943,12 @@
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr"/>
-      <c r="H22" s="24" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="I22" s="25" t="inlineStr">

--- a/web/files/九龙-启德-天玺．天第2期.xlsx
+++ b/web/files/九龙-启德-天玺．天第2期.xlsx
@@ -7996,7 +7996,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -26519,38 +26519,30 @@
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H392" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I392" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H392" s="5" t="n">
+        <v>14195000</v>
+      </c>
+      <c r="I392" s="5" t="n">
+        <v>29697</v>
       </c>
       <c r="J392" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K392" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L392" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K392" s="5" t="n">
+        <v>14195000</v>
+      </c>
+      <c r="L392" s="5" t="n">
+        <v>29697</v>
       </c>
       <c r="M392" s="3" t="inlineStr">
         <is>
@@ -26559,7 +26551,7 @@
       </c>
       <c r="N392" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28483,38 +28475,30 @@
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H422" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I422" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H422" s="5" t="n">
+        <v>13747140</v>
+      </c>
+      <c r="I422" s="5" t="n">
+        <v>28760</v>
       </c>
       <c r="J422" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K422" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L422" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K422" s="5" t="n">
+        <v>13747140</v>
+      </c>
+      <c r="L422" s="5" t="n">
+        <v>28760</v>
       </c>
       <c r="M422" s="3" t="inlineStr">
         <is>
@@ -28523,7 +28507,7 @@
       </c>
       <c r="N422" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -29135,7 +29119,7 @@
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
@@ -34522,7 +34506,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H513" s="5" t="n">
@@ -38534,7 +38518,7 @@
       </c>
       <c r="G575" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H575" s="5" t="n">
@@ -40759,7 +40743,7 @@
           <t>A1 | 908呎 (4+房)
 $4302万
 $47,378/呎
-(26年-07月-30日)</t>
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -41098,7 +41082,7 @@
           <t>A1 | 908呎 (4+房)
 $4094万
 $45,093/呎
-(26年-07月-23日)</t>
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -42867,7 +42851,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -42877,12 +42861,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -43943,12 +43927,12 @@
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr"/>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="23" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1420万
+$29,697/呎
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="I22" s="25" t="inlineStr">
@@ -44228,12 +44212,12 @@
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr"/>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H25" s="23" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1375万
+$28,760/呎
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="I25" s="25" t="inlineStr">
@@ -44323,12 +44307,12 @@
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr"/>
-      <c r="H26" s="24" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="I26" s="25" t="inlineStr">
@@ -45079,7 +45063,7 @@
           <t>A5 | 545呎 (2房)
 $1900万
 $34,859/呎
-(26年-07月-30日)</t>
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr"/>
@@ -45633,7 +45617,7 @@
           <t>A2 | 446呎 (2房)
 $1423万
 $31,901/呎
-(26年-07月-18日)</t>
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">

--- a/web/files/九龙-启德-天玺．天第2期.xlsx
+++ b/web/files/九龙-启德-天玺．天第2期.xlsx
@@ -7665,7 +7665,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -7673,31 +7673,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H107" s="5" t="n">
-        <v>15678800</v>
-      </c>
-      <c r="I107" s="5" t="n">
-        <v>32529</v>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="K107" s="5" t="n">
-        <v>15208436</v>
-      </c>
-      <c r="L107" s="5" t="n">
-        <v>31553</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>360日付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N107" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9233,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -9233,31 +9241,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H131" s="5" t="n">
-        <v>15501800</v>
-      </c>
-      <c r="I131" s="5" t="n">
-        <v>32161</v>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="K131" s="5" t="n">
-        <v>15036746</v>
-      </c>
-      <c r="L131" s="5" t="n">
-        <v>31197</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
-          <t>360日付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N131" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11943,7 +11959,7 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -17433,7 +17449,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -17443,12 +17459,12 @@
       </c>
       <c r="H255" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I255" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J255" s="3" t="inlineStr">
@@ -17458,12 +17474,12 @@
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L255" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr">
@@ -17473,7 +17489,7 @@
       </c>
       <c r="N255" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19871,38 +19887,30 @@
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H292" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I292" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H292" s="5" t="n">
+        <v>34331000</v>
+      </c>
+      <c r="I292" s="5" t="n">
+        <v>37809</v>
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K292" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L292" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K292" s="5" t="n">
+        <v>34331000</v>
+      </c>
+      <c r="L292" s="5" t="n">
+        <v>37809</v>
       </c>
       <c r="M292" s="3" t="inlineStr">
         <is>
@@ -19911,7 +19919,7 @@
       </c>
       <c r="N292" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -24116,7 +24124,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -25851,38 +25859,30 @@
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H382" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I382" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H382" s="5" t="n">
+        <v>14299000</v>
+      </c>
+      <c r="I382" s="5" t="n">
+        <v>29914</v>
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K382" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L382" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K382" s="5" t="n">
+        <v>14299000</v>
+      </c>
+      <c r="L382" s="5" t="n">
+        <v>29914</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
       </c>
       <c r="N382" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -29119,38 +29119,30 @@
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H432" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I432" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H432" s="5" t="n">
+        <v>13976800</v>
+      </c>
+      <c r="I432" s="5" t="n">
+        <v>29240</v>
       </c>
       <c r="J432" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K432" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L432" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K432" s="5" t="n">
+        <v>13976800</v>
+      </c>
+      <c r="L432" s="5" t="n">
+        <v>29240</v>
       </c>
       <c r="M432" s="3" t="inlineStr">
         <is>
@@ -29159,7 +29151,7 @@
       </c>
       <c r="N432" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -29189,38 +29181,30 @@
       </c>
       <c r="F433" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H433" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I433" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H433" s="5" t="n">
+        <v>20698000</v>
+      </c>
+      <c r="I433" s="5" t="n">
+        <v>37978</v>
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K433" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L433" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K433" s="5" t="n">
+        <v>20698000</v>
+      </c>
+      <c r="L433" s="5" t="n">
+        <v>37978</v>
       </c>
       <c r="M433" s="3" t="inlineStr">
         <is>
@@ -29229,7 +29213,7 @@
       </c>
       <c r="N433" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29846,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -29994,7 +29978,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -31325,7 +31309,7 @@
       </c>
       <c r="F465" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G465" s="3" t="inlineStr">
@@ -31796,7 +31780,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -32521,7 +32505,7 @@
       </c>
       <c r="F483" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G483" s="3" t="inlineStr">
@@ -32661,7 +32645,7 @@
       </c>
       <c r="F485" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G485" s="3" t="inlineStr">
@@ -32671,12 +32655,12 @@
       </c>
       <c r="H485" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I485" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J485" s="3" t="inlineStr">
@@ -32686,12 +32670,12 @@
       </c>
       <c r="K485" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L485" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M485" s="3" t="inlineStr">
@@ -32701,7 +32685,7 @@
       </c>
       <c r="N485" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -33854,7 +33838,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H503" s="5" t="n">
@@ -33981,7 +33965,7 @@
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G505" s="3" t="inlineStr">
@@ -33991,12 +33975,12 @@
       </c>
       <c r="H505" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I505" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J505" s="3" t="inlineStr">
@@ -34006,12 +33990,12 @@
       </c>
       <c r="K505" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L505" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M505" s="3" t="inlineStr">
@@ -34021,7 +34005,7 @@
       </c>
       <c r="N505" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -35285,7 +35269,7 @@
       </c>
       <c r="F525" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G525" s="3" t="inlineStr">
@@ -35295,12 +35279,12 @@
       </c>
       <c r="H525" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I525" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J525" s="3" t="inlineStr">
@@ -35310,12 +35294,12 @@
       </c>
       <c r="K525" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L525" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M525" s="3" t="inlineStr">
@@ -35325,7 +35309,7 @@
       </c>
       <c r="N525" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -36594,7 +36578,7 @@
       </c>
       <c r="G545" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H545" s="5" t="n">
@@ -37238,7 +37222,7 @@
       </c>
       <c r="G555" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H555" s="5" t="n">
@@ -37680,7 +37664,7 @@
       </c>
       <c r="G562" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H562" s="5" t="n">
@@ -37742,7 +37726,7 @@
       </c>
       <c r="G563" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H563" s="5" t="n">
@@ -37874,7 +37858,7 @@
       </c>
       <c r="G565" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H565" s="5" t="n">
@@ -38316,7 +38300,7 @@
       </c>
       <c r="G572" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H572" s="5" t="n">
@@ -39353,27 +39337,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>139</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
     </row>
@@ -40779,12 +40763,12 @@
 (25年-12月-23日)</t>
         </is>
       </c>
-      <c r="I24" s="25" t="inlineStr">
+      <c r="I24" s="24" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
-$1568万
-$32,529/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
@@ -41005,12 +40989,12 @@
 (25年-12月-03日)</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I26" s="24" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
-$1550万
-$32,161/呎
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -41303,12 +41287,12 @@
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr"/>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -42102,12 +42086,12 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D36" s="24" t="inlineStr">
         <is>
           <t>A2 | 450呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -42433,12 +42417,12 @@
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr"/>
-      <c r="C39" s="22" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>A1 | 908呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$3433万
+$37,809/呎
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="D39" s="24" t="inlineStr">
@@ -42851,7 +42835,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -42861,17 +42845,17 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>117</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>98</t>
         </is>
       </c>
     </row>
@@ -43485,7 +43469,7 @@
           <t>A | 1985呎 (4+房)
 $8243万
 $41,526/呎
-(26年-07月-31日)</t>
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr"/>
@@ -43832,12 +43816,12 @@
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr"/>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="23" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1430万
+$29,914/呎
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="I21" s="25" t="inlineStr">
@@ -44298,21 +44282,21 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$2070万
+$37,978/呎
+(26年-08月-21日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr"/>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="23" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1398万
+$29,240/呎
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="I26" s="25" t="inlineStr">
@@ -44382,7 +44366,7 @@
           <t>A2 | 446呎 (2房)
 $1688万
 $37,848/呎
-(26年-07月-30日)</t>
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -44398,7 +44382,7 @@
           <t>A5 | 545呎 (2房)
 $2015万
 $36,978/呎
-(26年-07月-23日)</t>
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr"/>
@@ -44567,12 +44551,12 @@
 (25年-11月-28日)</t>
         </is>
       </c>
-      <c r="D29" s="24" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -44692,7 +44676,7 @@
           <t>B1 | 478呎 (2房)
 $1243万
 $26,000/呎
-(26年-07月-23日)</t>
+(26年-08月-19日)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -44757,28 +44741,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 443呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>A3 | 443呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="24" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr"/>
@@ -44947,12 +44931,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D33" s="24" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -44968,7 +44952,7 @@
           <t>A5 | 545呎 (2房)
 $1973万
 $36,200/呎
-(26年-08月-06日)</t>
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr"/>
@@ -45137,12 +45121,12 @@
 (25年-12月-12日)</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
+      <c r="D35" s="24" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -45332,7 +45316,7 @@
           <t>A2 | 446呎 (2房)
 $1469万
 $32,937/呎
-(26年-07月-23日)</t>
+(26年-08月-20日)</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -45427,7 +45411,7 @@
           <t>A2 | 446呎 (2房)
 $1472万
 $33,013/呎
-(26年-07月-30日)</t>
+(26年-08月-21日)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -45522,7 +45506,7 @@
           <t>A2 | 446呎 (2房)
 $1451万
 $32,525/呎
-(26年-07月-30日)</t>
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
@@ -45538,7 +45522,7 @@
           <t>A5 | 545呎 (2房)
 $1707万
 $31,325/呎
-(26年-07月-30日)</t>
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr"/>
@@ -45547,7 +45531,7 @@
           <t>B1 | 478呎 (2房)
 $1192万
 $24,937/呎
-(26年-07月-30日)</t>
+(26年-08月-19日)</t>
         </is>
       </c>
       <c r="I39" s="22" t="inlineStr">
@@ -45642,7 +45626,7 @@
           <t>B1 | 478呎 (2房)
 $1178万
 $24,644/呎
-(26年-07月-19日)</t>
+(26年-08月-19日)</t>
         </is>
       </c>
       <c r="I40" s="23" t="inlineStr">

--- a/web/files/九龙-启德-天玺．天第2期.xlsx
+++ b/web/files/九龙-启德-天玺．天第2期.xlsx
@@ -18249,38 +18249,30 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H267" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I267" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="H267" s="5" t="n">
+        <v>15442940</v>
+      </c>
+      <c r="I267" s="5" t="n">
+        <v>34318</v>
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K267" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L267" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K267" s="5" t="n">
+        <v>15442940</v>
+      </c>
+      <c r="L267" s="5" t="n">
+        <v>34318</v>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
@@ -18289,7 +18281,7 @@
       </c>
       <c r="N267" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -21469,7 +21461,7 @@
       </c>
       <c r="F317" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -26581,38 +26573,30 @@
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H393" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I393" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="H393" s="5" t="n">
+        <v>21160000</v>
+      </c>
+      <c r="I393" s="5" t="n">
+        <v>38826</v>
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K393" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L393" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K393" s="5" t="n">
+        <v>21160000</v>
+      </c>
+      <c r="L393" s="5" t="n">
+        <v>38826</v>
       </c>
       <c r="M393" s="3" t="inlineStr">
         <is>
@@ -26621,7 +26605,7 @@
       </c>
       <c r="N393" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -27844,7 +27828,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -28542,7 +28526,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -32435,38 +32419,30 @@
       </c>
       <c r="F482" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H482" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I482" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="H482" s="5" t="n">
+        <v>13624000</v>
+      </c>
+      <c r="I482" s="5" t="n">
+        <v>28502</v>
       </c>
       <c r="J482" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K482" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L482" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K482" s="5" t="n">
+        <v>13624000</v>
+      </c>
+      <c r="L482" s="5" t="n">
+        <v>28502</v>
       </c>
       <c r="M482" s="3" t="inlineStr">
         <is>
@@ -32475,7 +32451,7 @@
       </c>
       <c r="N482" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -33313,38 +33289,30 @@
       </c>
       <c r="F495" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H495" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I495" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="H495" s="5" t="n">
+        <v>15800000</v>
+      </c>
+      <c r="I495" s="5" t="n">
+        <v>35426</v>
       </c>
       <c r="J495" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K495" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L495" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K495" s="5" t="n">
+        <v>15800000</v>
+      </c>
+      <c r="L495" s="5" t="n">
+        <v>35426</v>
       </c>
       <c r="M495" s="3" t="inlineStr">
         <is>
@@ -33353,7 +33321,7 @@
       </c>
       <c r="N495" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -36446,7 +36414,7 @@
       </c>
       <c r="G543" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H543" s="5" t="n">
@@ -39347,12 +39315,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -42199,12 +42167,12 @@
 (26年-07月-23日)</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D37" s="23" t="inlineStr">
         <is>
           <t>A2 | 450呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1544万
+$34,318/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="E37" s="25" t="inlineStr">
@@ -42835,7 +42803,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -42845,12 +42813,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>120</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -42984,12 +42952,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="Q5" s="24" t="inlineStr">
+      <c r="Q5" s="22" t="inlineStr">
         <is>
           <t>PSH B | 3553呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="R5" s="20" t="inlineStr"/>
@@ -43902,12 +43870,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F22" s="24" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
-招标单位
--
-(在售)</t>
+$2116万
+$38,826/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr"/>
@@ -44106,7 +44074,7 @@
           <t>B1 | 478呎 (2房)
 $1305万
 $27,309/呎
-(26年-07月-23日)</t>
+(26年-08月-26日)</t>
         </is>
       </c>
       <c r="I24" s="25" t="inlineStr">
@@ -44192,7 +44160,7 @@
           <t>A5 | 545呎 (2房)
 $2038万
 $37,394/呎
-(26年-08月-06日)</t>
+(26年-08月-26日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr"/>
@@ -44766,12 +44734,12 @@
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr"/>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H31" s="23" t="inlineStr">
         <is>
           <t>B1 | 478呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1362万
+$28,502/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -44836,12 +44804,12 @@
 (25年-11月-28日)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1580万
+$35,426/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -45332,7 +45300,7 @@
           <t>A5 | 545呎 (2房)
 $1738万
 $31,888/呎
-(26年-07月-23日)</t>
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr"/>

--- a/web/files/九龙-启德-天玺．天第2期.xlsx
+++ b/web/files/九龙-启德-天玺．天第2期.xlsx
@@ -7005,7 +7005,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="H191" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I191" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J191" s="3" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L191" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M191" s="3" t="inlineStr">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="N191" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -35237,7 +35237,7 @@
       </c>
       <c r="F525" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G525" s="3" t="inlineStr">
@@ -39305,7 +39305,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39320,12 +39320,12 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>128</t>
         </is>
       </c>
     </row>
@@ -40601,12 +40601,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="24" t="inlineStr">
         <is>
           <t>A5 | 612呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr"/>
@@ -40731,12 +40731,12 @@
 (25年-12月-23日)</t>
         </is>
       </c>
-      <c r="I24" s="24" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
@@ -41486,7 +41486,7 @@
           <t>A1 | 908呎 (4+房)
 $3554万
 $39,143/呎
-(26年-08月-06日)</t>
+(26年-08月-27日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -41522,12 +41522,12 @@
 (25年-12月-03日)</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
+      <c r="I31" s="24" t="inlineStr">
         <is>
           <t>B10 | 482呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="J31" s="23" t="inlineStr">
@@ -42803,7 +42803,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -42818,7 +42818,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -45089,12 +45089,12 @@
 (25年-12月-12日)</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">

--- a/web/files/九龙-启德-天玺．天第2期.xlsx
+++ b/web/files/九龙-启德-天玺．天第2期.xlsx
@@ -18316,7 +18316,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -35040,7 +35040,7 @@
       </c>
       <c r="G522" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H522" s="5" t="n">
@@ -35902,7 +35902,7 @@
       </c>
       <c r="G535" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H535" s="5" t="n">
@@ -36352,7 +36352,7 @@
       </c>
       <c r="G542" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H542" s="5" t="n">
@@ -42164,7 +42164,7 @@
           <t>A1 | 908呎 (4+房)
 $3357万
 $36,969/呎
-(26年-07月-23日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
@@ -45119,7 +45119,7 @@
           <t>B1 | 478呎 (2房)
 $1224万
 $25,597/呎
-(26年-07月-30日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="I35" s="23" t="inlineStr">
@@ -45189,7 +45189,7 @@
           <t>A2 | 446呎 (2房)
 $1508万
 $33,818/呎
-(26年-08月-06日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -45309,7 +45309,7 @@
           <t>B1 | 478呎 (2房)
 $1212万
 $25,356/呎
-(26年-07月-30日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="I37" s="23" t="inlineStr">

--- a/web/files/九龙-启德-天玺．天第2期.xlsx
+++ b/web/files/九龙-启德-天玺．天第2期.xlsx
@@ -9572,7 +9572,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -19884,7 +19884,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -21404,7 +21404,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -29108,7 +29108,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -31104,7 +31104,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -31166,7 +31166,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -31293,38 +31293,30 @@
       </c>
       <c r="F465" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H465" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I465" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H465" s="5" t="n">
+        <v>16493500</v>
+      </c>
+      <c r="I465" s="5" t="n">
+        <v>36981</v>
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K465" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L465" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K465" s="5" t="n">
+        <v>16493500</v>
+      </c>
+      <c r="L465" s="5" t="n">
+        <v>36981</v>
       </c>
       <c r="M465" s="3" t="inlineStr">
         <is>
@@ -31333,7 +31325,7 @@
       </c>
       <c r="N465" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -32481,38 +32473,30 @@
       </c>
       <c r="F483" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H483" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I483" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H483" s="5" t="n">
+        <v>20438000</v>
+      </c>
+      <c r="I483" s="5" t="n">
+        <v>37501</v>
       </c>
       <c r="J483" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K483" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L483" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K483" s="5" t="n">
+        <v>20438000</v>
+      </c>
+      <c r="L483" s="5" t="n">
+        <v>37501</v>
       </c>
       <c r="M483" s="3" t="inlineStr">
         <is>
@@ -32521,7 +32505,7 @@
       </c>
       <c r="N483" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38912,7 +38896,7 @@
       </c>
       <c r="G582" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H582" s="5" t="n">
@@ -40921,7 +40905,7 @@
           <t>A1 | 908呎 (4+房)
 $4193万
 $46,177/呎
-(26年-08月-11日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -42390,7 +42374,7 @@
           <t>A1 | 908呎 (4+房)
 $3433万
 $37,809/呎
-(26年-08月-18日)</t>
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="D39" s="24" t="inlineStr">
@@ -42616,7 +42600,7 @@
           <t>A1 | 908呎 (4+房)
 $3110万
 $34,251/呎
-(26年-07月-30日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
@@ -42813,12 +42797,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -44264,7 +44248,7 @@
           <t>B1 | 478呎 (2房)
 $1398万
 $29,240/呎
-(26年-08月-18日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="I26" s="25" t="inlineStr">
@@ -44519,12 +44503,12 @@
 (25年-11月-28日)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>A2 | 446呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$1649万
+$36,981/呎
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -44540,7 +44524,7 @@
           <t>A5 | 545呎 (2房)
 $2021万
 $37,085/呎
-(26年-08月-11日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr"/>
@@ -44549,7 +44533,7 @@
           <t>B1 | 478呎 (2房)
 $1250万
 $26,151/呎
-(26年-08月-06日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -44725,12 +44709,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>A5 | 545呎 (2房)
-招标单位
--
-(暂停销售)</t>
+$2044万
+$37,501/呎
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr"/>
@@ -45689,7 +45673,7 @@
           <t>B1 | 478呎 (2房)
 $1170万
 $24,481/呎
-(26年-08月-06日)</t>
+(26年-09月-01日)</t>
         </is>
       </c>
       <c r="I41" s="23" t="inlineStr">

--- a/web/files/九龙-启德-天玺．天第2期.xlsx
+++ b/web/files/九龙-启德-天玺．天第2期.xlsx
@@ -28464,7 +28464,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -44153,7 +44153,7 @@
           <t>B1 | 478呎 (2房)
 $1375万
 $28,760/呎
-(26年-08月-14日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="I25" s="25" t="inlineStr">
